--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.023</v>
+        <v>0.227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="E7" t="n">
-        <v>0.012</v>
+        <v>0.203</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.074</v>
+        <v>-0.143</v>
       </c>
       <c r="D8" t="n">
         <v>-0.042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.025</v>
+        <v>-0.002</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.018</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.392</v>
+        <v>-0.024</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="E10" t="n">
-        <v>0.362</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.024</v>
+        <v>0.107</v>
       </c>
       <c r="D12" t="n">
-        <v>0.027</v>
+        <v>0.042</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.113</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.049</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.064</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.034</v>
+        <v>-0.128</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>0.018</v>
       </c>
       <c r="E14" t="n">
-        <v>0.026</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.027</v>
+        <v>-0.012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.027</v>
+        <v>-0.007</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>0.032</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.046</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.044</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.008</v>
+        <v>0.392</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.002</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>0.362</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.042</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.101</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.401</v>
+        <v>0.197</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.038</v>
+        <v>0.067</v>
       </c>
       <c r="E20" t="n">
-        <v>0.363</v>
+        <v>0.13</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D21" t="n">
-        <v>0.042</v>
+        <v>-0.042</v>
       </c>
       <c r="E21" t="n">
-        <v>0.065</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.128</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.018</v>
+        <v>-0.049</v>
       </c>
       <c r="E22" t="n">
-        <v>0.11</v>
+        <v>0.064</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="D23" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.197</v>
+        <v>-0.401</v>
       </c>
       <c r="D24" t="n">
-        <v>0.067</v>
+        <v>-0.038</v>
       </c>
       <c r="E24" t="n">
-        <v>0.13</v>
+        <v>0.363</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.077</v>
+        <v>0.041</v>
       </c>
       <c r="D25" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="E25" t="n">
-        <v>0.046</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.032</v>
+        <v>0.077</v>
       </c>
       <c r="D26" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.041</v>
+        <v>-0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.012</v>
+        <v>-0.057</v>
       </c>
       <c r="E27" t="n">
-        <v>0.029</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.041</v>
+        <v>-0.041</v>
       </c>
       <c r="D28" t="n">
-        <v>0.037</v>
+        <v>-0.012</v>
       </c>
       <c r="E28" t="n">
-        <v>0.004000000000000004</v>
+        <v>0.029</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.066</v>
+        <v>0.022</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.057</v>
+        <v>0.015</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.046</v>
+        <v>-0.054</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="E30" t="n">
-        <v>0.044</v>
+        <v>0.027</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.227</v>
+        <v>-0.019</v>
       </c>
       <c r="D31" t="n">
-        <v>0.024</v>
+        <v>-0.024</v>
       </c>
       <c r="E31" t="n">
-        <v>0.203</v>
+        <v>-0.005000000000000001</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.024</v>
+        <v>-0.003</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.005000000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.005</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.012</v>
+        <v>-0.005</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1424,13 +1424,13 @@
         <v>0.132000111260347</v>
       </c>
       <c r="E2" t="n">
-        <v>1.667164261064091</v>
+        <v>1.66716426106409</v>
       </c>
       <c r="F2" t="n">
         <v>1.124233559763564</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66557429911799</v>
+        <v>1.665574299117989</v>
       </c>
     </row>
   </sheetData>
@@ -1494,16 +1494,16 @@
         <v>1.748744200678083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09972246735547884</v>
+        <v>0.0997224673554809</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553291756211874</v>
+        <v>1.553291756211869</v>
       </c>
       <c r="E2" t="n">
-        <v>1.944196645144293</v>
+        <v>1.944196645144297</v>
       </c>
       <c r="F2" t="n">
-        <v>7.59513082973068e-69</v>
+        <v>7.59513082977984e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02958633974415711</v>
+        <v>0.0295863397441571</v>
       </c>
       <c r="C3" t="n">
         <v>0.01822177522012755</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.006127683421677306</v>
+        <v>-0.006127683421677316</v>
       </c>
       <c r="E3" t="n">
         <v>0.06530036290999153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1044440307699912</v>
+        <v>0.1044440307699914</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09784011424187247</v>
+        <v>0.0978401142418725</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04951895669896676</v>
+        <v>0.04951895669896678</v>
       </c>
       <c r="D4" t="n">
         <v>0.0007847425598991736</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01273797200940392</v>
+        <v>-0.0127379720094039</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03343233284250817</v>
+        <v>0.03343233284250818</v>
       </c>
       <c r="D5" t="n">
         <v>-0.07826414029987555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05278819628106771</v>
+        <v>0.05278819628106774</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7031976288909341</v>
+        <v>0.7031976288909345</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04927628124940888</v>
+        <v>0.04927628124940879</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03239456843861484</v>
+        <v>0.03239456843861483</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01421590618499414</v>
+        <v>-0.01421590618499421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1127684686838119</v>
+        <v>0.1127684686838118</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1282277489991771</v>
+        <v>0.1282277489991777</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01047785258090151</v>
+        <v>0.0104778525809015</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03252233317855409</v>
+        <v>0.03252233317855407</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05326474914227656</v>
+        <v>-0.05326474914227652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07422045430407957</v>
+        <v>0.07422045430407953</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7473208240704078</v>
+        <v>0.7473208240704079</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06433271843302672</v>
+        <v>0.06433271843302669</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03291080729184541</v>
+        <v>0.03291080729184542</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001712785611284739</v>
+        <v>-0.0001712785611285156</v>
       </c>
       <c r="E8" t="n">
         <v>0.1288367154271819</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0506114447635788</v>
+        <v>0.05061144476357895</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02865140490375858</v>
+        <v>0.0286514049037586</v>
       </c>
       <c r="C9" t="n">
         <v>0.03191029283342593</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03389161978588283</v>
+        <v>-0.03389161978588281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09119442959339998</v>
+        <v>0.09119442959340002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3692530175492089</v>
+        <v>0.3692530175492086</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0009794214476963451</v>
+        <v>-0.0009794214476963237</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05063414819939266</v>
+        <v>0.05063414819939274</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1002205283063696</v>
+        <v>-0.1002205283063697</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09826168541097689</v>
+        <v>0.09826168541097707</v>
       </c>
       <c r="F10" t="n">
-        <v>0.984567400646319</v>
+        <v>0.9845674006463193</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01946826154009417</v>
+        <v>0.01946826154009435</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05194685720438132</v>
+        <v>0.05194685720438134</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08234570769053826</v>
+        <v>-0.08234570769053812</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1212822307707266</v>
+        <v>0.1212822307707268</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7078295534164005</v>
+        <v>0.707829553416398</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06785609067849571</v>
+        <v>0.06785609067849589</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05163905582747093</v>
+        <v>0.05163905582747092</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0333545989390005</v>
+        <v>-0.03335459893900031</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1690667802959919</v>
+        <v>0.1690667802959921</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1888307512048429</v>
+        <v>0.1888307512048417</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04035183396023298</v>
+        <v>0.04035183396023317</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05171295167094472</v>
+        <v>0.05171295167094477</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06100368884907909</v>
+        <v>-0.06100368884907898</v>
       </c>
       <c r="E13" t="n">
-        <v>0.141707356769545</v>
+        <v>0.1417073567695453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4352118346691944</v>
+        <v>0.4352118346691926</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01360432138726275</v>
+        <v>0.01360432138726268</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05321733263316389</v>
+        <v>0.05321733263316392</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09069973392702659</v>
+        <v>-0.09069973392702671</v>
       </c>
       <c r="E14" t="n">
         <v>0.1179083767015521</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7982311147396448</v>
+        <v>0.7982311147396461</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05405252017528367</v>
+        <v>0.05405252017528384</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05226735188844168</v>
+        <v>0.0522673518884417</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04838960709334361</v>
+        <v>-0.04838960709334347</v>
       </c>
       <c r="E15" t="n">
-        <v>0.156494647443911</v>
+        <v>0.1564946474439111</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3010639142436649</v>
+        <v>0.3010639142436634</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04086477158037331</v>
+        <v>0.04086477158037348</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05309945880834843</v>
+        <v>0.05309945880834849</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06320825528255775</v>
+        <v>-0.06320825528255769</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1449377984433044</v>
+        <v>0.1449377984433046</v>
       </c>
       <c r="F16" t="n">
-        <v>0.441543596089689</v>
+        <v>0.4415435960896876</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01102820644228588</v>
+        <v>0.01102820644228603</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05158345722977694</v>
+        <v>0.05158345722977693</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0900735119261392</v>
+        <v>-0.09007351192613902</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1121299248107109</v>
+        <v>0.1121299248107111</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8307081155011091</v>
+        <v>0.8307081155011068</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02900589471309407</v>
+        <v>0.02900589471309431</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04992506750994714</v>
+        <v>0.04992506750994722</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06884543953213311</v>
+        <v>-0.06884543953213304</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1268572289583212</v>
+        <v>0.1268572289583217</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5612481417346374</v>
+        <v>0.561248141734635</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00970689381671991</v>
+        <v>0.009706893816720148</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05188944681346105</v>
+        <v>0.05188944681346103</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09199455311537043</v>
+        <v>-0.09199455311537015</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1114083407488102</v>
+        <v>0.1114083407488104</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8516067315648262</v>
+        <v>0.8516067315648226</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01294184623909382</v>
+        <v>-0.01294184623909369</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04979214122466381</v>
+        <v>0.04979214122466382</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.110532649752567</v>
+        <v>-0.1105326497525669</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08464895727437935</v>
+        <v>0.08464895727437949</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7949274527428531</v>
+        <v>0.7949274527428551</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004450654511219671</v>
+        <v>0.00445065451121985</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05125308284729293</v>
+        <v>0.051253082847293</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09600354196612207</v>
+        <v>-0.09600354196612203</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1049048509885614</v>
+        <v>0.1049048509885617</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9308012234128848</v>
+        <v>0.9308012234128822</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01178950629292731</v>
+        <v>0.0117895062929274</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05351780370106504</v>
+        <v>0.05351780370106509</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0931034614928446</v>
+        <v>-0.09310346149284458</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1166824740786992</v>
+        <v>0.1166824740786994</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8256442990935591</v>
+        <v>0.8256442990935577</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04500853091113247</v>
+        <v>0.0450085309111327</v>
       </c>
       <c r="C23" t="n">
         <v>0.05073676871697227</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05443370846607168</v>
+        <v>-0.05443370846607145</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1444507702883366</v>
+        <v>0.1444507702883368</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3750256648141908</v>
+        <v>0.3750256648141884</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09317839536589109</v>
+        <v>0.09317839536589106</v>
       </c>
       <c r="C24" t="n">
         <v>0.04199057011256823</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01087839025495335</v>
+        <v>0.01087839025495332</v>
       </c>
       <c r="E24" t="n">
         <v>0.1754784004768288</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0264845855049597</v>
+        <v>0.02648458550495973</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03623225650076148</v>
+        <v>0.03623225650076144</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02486297432359932</v>
+        <v>0.02486297432359926</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01249827772203729</v>
+        <v>-0.01249827772203721</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08496279072356025</v>
+        <v>0.0849627907235601</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1450397569591434</v>
+        <v>0.1450397569591428</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01467109228439215</v>
+        <v>0.01467109228439205</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02811127962746577</v>
+        <v>0.02811127962746578</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04042600334477531</v>
+        <v>-0.04042600334477542</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06976818791355961</v>
+        <v>0.06976818791355952</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6017445295692663</v>
+        <v>0.6017445295692687</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03310111763713026</v>
+        <v>-0.03310111763713031</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920545388089278</v>
+        <v>0.02920545388089281</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09034275539582565</v>
+        <v>-0.09034275539582576</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02414052012156514</v>
+        <v>0.02414052012156515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2570512552489407</v>
+        <v>0.2570512552489402</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01368596077233372</v>
+        <v>-0.01368596077233375</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02963823096954</v>
+        <v>0.02963823096954001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07177582603811176</v>
+        <v>-0.07177582603811181</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04440390449344433</v>
+        <v>0.04440390449344431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6442483269078485</v>
+        <v>0.6442483269078476</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02682587599480332</v>
+        <v>-0.02682587599480334</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02937399338914296</v>
+        <v>0.02937399338914297</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08439784511964117</v>
+        <v>-0.0843978451196412</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03074609313003453</v>
+        <v>0.03074609313003451</v>
       </c>
       <c r="F29" t="n">
-        <v>0.361109702580204</v>
+        <v>0.3611097025802037</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2191,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3985398745276545</v>
+        <v>0.3985398745276548</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03933933271771811</v>
+        <v>0.03933933271771812</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3214361992250888</v>
+        <v>0.321436199225089</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4756435498302203</v>
+        <v>0.4756435498302205</v>
       </c>
       <c r="F30" t="n">
-        <v>4.032349524444153e-24</v>
+        <v>4.032349524444008e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4977006363722659</v>
+        <v>-0.002088076448677743</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01226810100606315</v>
+        <v>0.001402263199247396</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4736556002416825</v>
+        <v>-0.004836461816048554</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5217456725028493</v>
+        <v>0.0006603089186930666</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1364673619490752</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2241,19 +2241,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001532654351402116</v>
+        <v>-0.001532654351402113</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001599885891944196</v>
+        <v>0.001599885891944229</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004668373078986481</v>
+        <v>-0.004668373078986541</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00160306437618225</v>
+        <v>0.001603064376182316</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3380742102093376</v>
+        <v>0.3380742102093481</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2269,16 +2269,16 @@
         <v>-0.003156716305439282</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00419143405202007</v>
+        <v>0.00419143405202006</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0113717760909734</v>
+        <v>-0.01137177609097338</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005058343480094839</v>
+        <v>0.00505834348009482</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4513687051621521</v>
+        <v>0.451368705162151</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001063121985276503</v>
+        <v>0.4977006363722659</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001289385890041366</v>
+        <v>0.01226810100606328</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.001464027921378696</v>
+        <v>0.4736556002416823</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003590271891931702</v>
+        <v>0.5217456725028495</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4096452440067871</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2319,7 +2319,7 @@
         <v>1.638429102143954</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04812377374195399</v>
+        <v>0.04812377374195412</v>
       </c>
       <c r="D35" t="n">
         <v>1.544108238809569</v>
@@ -2328,7 +2328,7 @@
         <v>1.732749965478338</v>
       </c>
       <c r="F35" t="n">
-        <v>4.628174711695116e-254</v>
+        <v>4.628174711708808e-254</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.002088076448677745</v>
+        <v>0.001063121985276503</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001402263199247399</v>
+        <v>0.001289385890041367</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.004836461816048561</v>
+        <v>-0.001464027921378699</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0006603089186930705</v>
+        <v>0.003590271891931705</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1364673619490757</v>
+        <v>0.4096452440067879</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.774614073588892</v>
+        <v>-2.774614073588889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5213956350107392</v>
+        <v>0.5213956350107419</v>
       </c>
       <c r="D2" t="n">
-        <v>1.029072958036696e-07</v>
+        <v>1.029072958036885e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02531896946916947</v>
+        <v>-0.02531896946916952</v>
       </c>
       <c r="C3" t="n">
         <v>0.1001870355608945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.800486891575911</v>
+        <v>0.8004868915759106</v>
       </c>
     </row>
     <row r="4">
@@ -2437,10 +2437,10 @@
         <v>0.2256150601556657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2336513202417124</v>
+        <v>0.2336513202417123</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3342414930584405</v>
+        <v>0.3342414930584404</v>
       </c>
     </row>
     <row r="5">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8160827895347564</v>
+        <v>0.8160827895347563</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734116198833068</v>
+        <v>0.1734116198833065</v>
       </c>
       <c r="D5" t="n">
-        <v>2.525694832362401e-06</v>
+        <v>2.525694832362313e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03622598517976088</v>
+        <v>0.03622598517976082</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1914953081760687</v>
+        <v>0.1914953081760685</v>
       </c>
       <c r="D6" t="n">
-        <v>0.849956232913377</v>
+        <v>0.8499562329133771</v>
       </c>
     </row>
     <row r="7">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2771938342360029</v>
+        <v>0.2771938342360028</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901314810930083</v>
+        <v>0.1901314810930081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.144866444211752</v>
+        <v>0.1448664442117519</v>
       </c>
     </row>
     <row r="8">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1053581304950988</v>
+        <v>0.1053581304950987</v>
       </c>
       <c r="C8" t="n">
-        <v>0.195344266715979</v>
+        <v>0.1953442667159787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5896481989107902</v>
+        <v>0.58964819891079</v>
       </c>
     </row>
     <row r="9">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8758696511293145</v>
+        <v>0.8758696511293144</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1693371735726044</v>
+        <v>0.1693371735726042</v>
       </c>
       <c r="D9" t="n">
-        <v>2.311788629896161e-07</v>
+        <v>2.31178862989609e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04427462059794664</v>
+        <v>-0.04427462059794676</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604040478124689</v>
+        <v>0.2604040478124681</v>
       </c>
       <c r="D10" t="n">
-        <v>0.864992220220115</v>
+        <v>0.8649922202201142</v>
       </c>
     </row>
     <row r="11">
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2742205061505733</v>
+        <v>-0.2742205061505736</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787689544694693</v>
+        <v>0.2787689544694695</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3252710045288593</v>
+        <v>0.3252710045288592</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08193295015444167</v>
+        <v>0.08193295015444108</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2597818841250333</v>
+        <v>0.2597818841250332</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7524645599189494</v>
+        <v>0.752464559918951</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03769699417328266</v>
+        <v>0.03769699417328217</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2573362415649833</v>
+        <v>0.2573362415649834</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8835351721093889</v>
+        <v>0.8835351721093905</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05102687086135001</v>
+        <v>-0.05102687086135054</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2608488036216077</v>
+        <v>0.2608488036216073</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8449087216020067</v>
+        <v>0.8449087216020048</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1194505179052276</v>
+        <v>0.1194505179052273</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572736242808299</v>
+        <v>0.2572736242808297</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6424373510261985</v>
+        <v>0.6424373510261991</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.003394520999804855</v>
+        <v>-0.003394520999805394</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383941217340666</v>
+        <v>0.2383941217340661</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9886392149415394</v>
+        <v>0.9886392149415375</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1051737680003749</v>
+        <v>0.1051737680003745</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2544989159147917</v>
+        <v>0.254498915914791</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6794174396292685</v>
+        <v>0.6794174396292689</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377738518166142</v>
+        <v>-0.1377738518166144</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2637734916431446</v>
+        <v>0.2637734916431439</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6014483864186199</v>
+        <v>0.6014483864186183</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02393490642264807</v>
+        <v>-0.02393490642264846</v>
       </c>
       <c r="C19" t="n">
         <v>0.2529805715426137</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9246233049950194</v>
+        <v>0.9246233049950183</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07301273583930003</v>
+        <v>-0.0730127358393004</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2675190900686552</v>
+        <v>0.267519090068655</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7849106151948615</v>
+        <v>0.7849106151948602</v>
       </c>
     </row>
     <row r="21">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2069135147918236</v>
+        <v>0.2069135147918232</v>
       </c>
       <c r="C21" t="n">
         <v>0.2442870989291297</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3969897777610721</v>
+        <v>0.396989777761073</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1717092932306342</v>
+        <v>-0.1717092932306348</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696190828094295</v>
+        <v>0.2696190828094297</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5242168027309888</v>
+        <v>0.5242168027309875</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5023322926397004</v>
+        <v>-0.5023322926397006</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2872431741192606</v>
+        <v>0.2872431741192604</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0803247361300542</v>
+        <v>0.08032473613005384</v>
       </c>
     </row>
     <row r="24">
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9363452786511915</v>
+        <v>0.9363452786511912</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483102369545481</v>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5780513937211161</v>
+        <v>-0.5780513937211164</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1144316984848931</v>
+        <v>0.1144316984848932</v>
       </c>
       <c r="D25" t="n">
-        <v>4.38360579780309e-07</v>
+        <v>4.383605797803144e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2362077053959268</v>
+        <v>0.2362077053959267</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1504768607120735</v>
+        <v>0.1504768607120733</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1164784602604649</v>
+        <v>0.1164784602604647</v>
       </c>
     </row>
     <row r="27">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04595559996241694</v>
+        <v>-0.04595559996241708</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1616567014228946</v>
+        <v>0.1616567014228947</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7761966040079389</v>
+        <v>0.7761966040079383</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07605967823822851</v>
+        <v>-0.07605967823822857</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1614891401822258</v>
+        <v>0.1614891401822257</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6376482824383382</v>
+        <v>0.6376482824383375</v>
       </c>
     </row>
     <row r="29">
@@ -2834,29 +2834,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0962698642640232</v>
+        <v>0.09626986426402311</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543844601757253</v>
+        <v>0.1543844601757254</v>
       </c>
       <c r="D29" t="n">
-        <v>0.532908543609379</v>
+        <v>0.5329085436093797</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0293709147194724</v>
+        <v>-0.00242675524240514</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06892977188933401</v>
+        <v>0.007136997489227798</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6700356258910086</v>
+        <v>0.7338379468830419</v>
       </c>
     </row>
     <row r="31">
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005017911290030906</v>
+        <v>-0.005017911290030937</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008305443072288868</v>
+        <v>0.008305443072289021</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5457296836910575</v>
+        <v>0.5457296836910623</v>
       </c>
     </row>
     <row r="32">
@@ -2882,29 +2882,29 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004305141260627509</v>
+        <v>-0.004305141260627533</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02221655124176761</v>
+        <v>0.02221655124176771</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8463475148043503</v>
+        <v>0.8463475148043501</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.006290302487114353</v>
+        <v>0.02937091471947223</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006868867616884194</v>
+        <v>0.06892977188933347</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3597875728110751</v>
+        <v>0.6700356258910081</v>
       </c>
     </row>
     <row r="34">
@@ -2914,29 +2914,29 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.324898498976664</v>
+        <v>0.3248984989766633</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2612255249732388</v>
+        <v>0.2612255249732386</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2135926414117484</v>
+        <v>0.2135926414117491</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.002426755242405132</v>
+        <v>0.006290302487114358</v>
       </c>
       <c r="C35" t="n">
-        <v>0.007136997489227802</v>
+        <v>0.006868867616884179</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7338379468830429</v>
+        <v>0.3597875728110738</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.001</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.096</v>
+        <v>-0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.079</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.059</v>
+        <v>0.033</v>
       </c>
       <c r="D8" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.028</v>
+        <v>0.006</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.021</v>
+        <v>0.006</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.033</v>
+        <v>-0.054</v>
       </c>
       <c r="D10" t="n">
-        <v>0.025</v>
+        <v>-0.023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008</v>
+        <v>0.031</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="D12" t="n">
-        <v>0.017</v>
+        <v>-0.006</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.044</v>
+        <v>0.185</v>
       </c>
       <c r="D13" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="E13" t="n">
-        <v>0.017</v>
+        <v>0.172</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.181</v>
+        <v>-0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>0.014</v>
+        <v>-0.028</v>
       </c>
       <c r="E14" t="n">
-        <v>0.167</v>
+        <v>-0.021</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.076</v>
+        <v>-0.09</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="E15" t="n">
-        <v>0.076</v>
+        <v>0.061</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006</v>
+        <v>-0.003000000000000001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.008</v>
+        <v>-0.096</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>0.017</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001</v>
+        <v>0.079</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.012</v>
+        <v>0.036</v>
       </c>
       <c r="D19" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.035</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.054</v>
+        <v>-0.008</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.023</v>
+        <v>-0.007</v>
       </c>
       <c r="E20" t="n">
-        <v>0.031</v>
+        <v>0.001</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.185</v>
+        <v>0.076</v>
       </c>
       <c r="D21" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.172</v>
+        <v>0.076</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.215</v>
+        <v>0.075</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.058</v>
+        <v>0.004</v>
       </c>
       <c r="E22" t="n">
-        <v>0.157</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.095</v>
+        <v>0.044</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005</v>
+        <v>0.027</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09</v>
+        <v>0.017</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.036</v>
+        <v>-0.015</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001</v>
+        <v>-0.03</v>
       </c>
       <c r="E26" t="n">
-        <v>0.035</v>
+        <v>-0.015</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.075</v>
+        <v>-0.181</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.392</v>
+        <v>-0.215</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.027</v>
+        <v>-0.058</v>
       </c>
       <c r="E29" t="n">
-        <v>0.365</v>
+        <v>0.157</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.015</v>
+        <v>-0.001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.03</v>
+        <v>-0.001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.09</v>
+        <v>-0.392</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.029</v>
+        <v>-0.027</v>
       </c>
       <c r="E32" t="n">
-        <v>0.061</v>
+        <v>0.365</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1629543857601319</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836644</v>
+        <v>1.864929480836645</v>
       </c>
       <c r="F2" t="n">
         <v>1.150690388380934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713846</v>
+        <v>1.864005612713847</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.493998113457369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.091541763420905</v>
+        <v>0.091541763420904</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071109</v>
+        <v>1.314579554071111</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843629</v>
+        <v>1.673416672843627</v>
       </c>
       <c r="F2" t="n">
-        <v>7.0672061530913e-60</v>
+        <v>7.067206153070735e-60</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,16 +1492,16 @@
         <v>0.01139734884641808</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870616</v>
+        <v>0.01836912354870614</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661258</v>
+        <v>-0.02460547173661254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04740016942944873</v>
+        <v>0.0474001694294487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931429</v>
+        <v>0.5349534598931425</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09369904833157605</v>
+        <v>-0.09369904833157608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04522288491293568</v>
+        <v>0.04522288491293567</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1823342740379298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005063822625222328</v>
+        <v>-0.005063822625222383</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03827115219154187</v>
+        <v>0.03827115219154174</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152957</v>
+        <v>-0.01066467357152959</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981982333274043</v>
+        <v>0.02981982333274041</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06911045332904797</v>
+        <v>-0.06911045332904796</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04778110618598883</v>
+        <v>0.04778110618598878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742433</v>
+        <v>0.7206149497742427</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04301492997829064</v>
+        <v>-0.04301492997829066</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03066350771200718</v>
+        <v>0.03066350771200715</v>
       </c>
       <c r="D6" t="n">
         <v>-0.1031143007334909</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690961</v>
+        <v>0.01708444077690956</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606749173778486</v>
+        <v>0.1606749173778481</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000958159133144383</v>
+        <v>0.000958159133144392</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02954143714616891</v>
+        <v>0.0295414371461689</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0569419937249004</v>
+        <v>-0.05694199372490037</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05885831199118917</v>
+        <v>0.05885831199118915</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875788</v>
+        <v>0.9741256203875786</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0149947185988891</v>
+        <v>-0.01499471859888912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603004</v>
+        <v>0.03011722069603003</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07402338647755231</v>
+        <v>-0.07402338647755233</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977411</v>
+        <v>0.04403394927977407</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956146</v>
+        <v>0.6185696367956139</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619061</v>
+        <v>0.009760945713619051</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955248</v>
+        <v>0.02969887927955246</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04844778805550666</v>
+        <v>-0.04844778805550663</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274478</v>
+        <v>0.06796967948274474</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7424098394948969</v>
+        <v>0.742409839494897</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057868</v>
+        <v>0.008945036718057971</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369303</v>
+        <v>0.05227344659369308</v>
       </c>
       <c r="D10" t="n">
         <v>-0.09350903595335844</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1113991093894742</v>
+        <v>0.1113991093894744</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8641293418452048</v>
+        <v>0.8641293418452034</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07294946240716804</v>
+        <v>-0.07294946240716803</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04956147246244856</v>
+        <v>0.04956147246244859</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1700881634543409</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0241892386400048</v>
+        <v>0.02418923864000487</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1410482591329774</v>
+        <v>0.1410482591329777</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0866234227437129</v>
+        <v>-0.08662342274371293</v>
       </c>
       <c r="C12" t="n">
         <v>0.05089844563154299</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1863825430506072</v>
+        <v>-0.1863825430506073</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318141</v>
+        <v>0.01313569756318138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08877648025963067</v>
+        <v>0.08877648025963054</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.008024749836484031</v>
+        <v>-0.008024749836484038</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05113295056969707</v>
+        <v>0.05113295056969714</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1082434913763571</v>
+        <v>-0.1082434913763573</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09219399170338906</v>
+        <v>0.0921939917033892</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942476</v>
+        <v>0.8752929892942477</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04340557759080313</v>
+        <v>-0.04340557759080326</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0504592946080262</v>
+        <v>0.0504592946080263</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1423039777078306</v>
+        <v>-0.142303977707831</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05549282252622437</v>
+        <v>0.05549282252622444</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082854</v>
+        <v>0.3896734268082849</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,16 +1789,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0457467153042766</v>
+        <v>-0.04574671530427658</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428279</v>
+        <v>0.04961392181428277</v>
       </c>
       <c r="D15" t="n">
         <v>-0.142988215192057</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350382</v>
+        <v>0.05149478458350379</v>
       </c>
       <c r="F15" t="n">
         <v>0.3565004068554806</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03713592023139941</v>
+        <v>-0.0371359202313994</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05010472347761164</v>
+        <v>0.05010472347761168</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1353393737028567</v>
+        <v>-0.1353393737028568</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06106753324005789</v>
+        <v>0.06106753324005798</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445322</v>
+        <v>0.4585927625445326</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01948239245873594</v>
+        <v>-0.0194823924587359</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05062347938805204</v>
+        <v>0.0506234793880521</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1187025888314237</v>
+        <v>-0.1187025888314238</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395184</v>
+        <v>0.07973780391395199</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7003493364163529</v>
+        <v>0.7003493364163539</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02897547644273368</v>
+        <v>-0.02897547644273366</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05100630816200024</v>
+        <v>0.05100630816200025</v>
       </c>
       <c r="D18" t="n">
         <v>-0.1289460034246055</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913818</v>
+        <v>0.07099505053913824</v>
       </c>
       <c r="F18" t="n">
-        <v>0.569983138127512</v>
+        <v>0.5699831381275126</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04008864287509659</v>
+        <v>-0.04008864287509657</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04996256722766795</v>
+        <v>0.04996256722766797</v>
       </c>
       <c r="D19" t="n">
         <v>-0.138013475216487</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0578361894662938</v>
+        <v>0.05783618946629387</v>
       </c>
       <c r="F19" t="n">
-        <v>0.422336903387222</v>
+        <v>0.4223369033872225</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662678</v>
+        <v>-0.08980962914662673</v>
       </c>
       <c r="C20" t="n">
         <v>0.04956030606584794</v>
@@ -1923,10 +1923,10 @@
         <v>-0.1869460440984707</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007326785805217145</v>
+        <v>0.007326785805217215</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06996638708640614</v>
+        <v>0.06996638708640632</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943027</v>
+        <v>0.003397924751943067</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773242</v>
+        <v>0.04891083189773249</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09246554422150538</v>
+        <v>-0.09246554422150546</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09926139372539144</v>
+        <v>0.09926139372539161</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446140588838091</v>
+        <v>0.9446140588838084</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.005820590202436488</v>
+        <v>-0.005820590202436582</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04992222605418412</v>
+        <v>0.04992222605418418</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967045</v>
+        <v>-0.1036663552967047</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09202517489183151</v>
+        <v>0.09202517489183154</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9071824564981807</v>
+        <v>0.9071824564981794</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1992,16 +1992,16 @@
         <v>-0.06091882540351704</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04983273321557466</v>
+        <v>0.04983273321557469</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1585891877572362</v>
+        <v>-0.1585891877572363</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020217</v>
+        <v>0.03675153695020222</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215314283124578</v>
+        <v>0.2215314283124579</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884725</v>
+        <v>-0.04546552218884724</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04088368473780891</v>
+        <v>0.04088368473780889</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1255960718302426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0346650274525481</v>
+        <v>0.03466502745254808</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958384</v>
+        <v>0.2661080237958383</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00585500374982147</v>
+        <v>0.005855003749821498</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273563</v>
+        <v>0.02357096913273561</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04034324683104566</v>
+        <v>-0.04034324683104561</v>
       </c>
       <c r="E25" t="n">
         <v>0.05205325433068861</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625452</v>
+        <v>0.8038257535625442</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02022035479316629</v>
+        <v>0.0202203547931664</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847209635064419</v>
+        <v>0.02847209635064421</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845062</v>
+        <v>-0.03558392861845055</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0760246382047832</v>
+        <v>0.07602463820478336</v>
       </c>
       <c r="F26" t="n">
-        <v>0.477591619887006</v>
+        <v>0.4775916198870037</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390033</v>
+        <v>0.01017504924390039</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0292081708218194</v>
+        <v>0.02920817082181943</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115936</v>
+        <v>-0.04707191362115938</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210896001</v>
+        <v>0.06742201210896015</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194186</v>
+        <v>0.7275675029194174</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0307527429121369</v>
+        <v>0.03075274291213697</v>
       </c>
       <c r="C28" t="n">
         <v>0.02852520938942747</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02515564014260472</v>
+        <v>-0.02515564014260466</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687853</v>
+        <v>0.08666112596687861</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2809935950997029</v>
+        <v>0.2809935950997019</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01431775187402592</v>
+        <v>-0.01431775187402586</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140895</v>
+        <v>0.02757795020140896</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622658</v>
+        <v>-0.06836954103622656</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817475</v>
+        <v>0.03973403728817484</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206329</v>
+        <v>0.6036394802206344</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.3642249454799706</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03859338896492541</v>
+        <v>0.03859338896492542</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2885832930673711</v>
+        <v>0.2885832930673712</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4398665978925698</v>
+        <v>0.43986659789257</v>
       </c>
       <c r="F30" t="n">
         <v>3.817947647451369e-21</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001854532319157671</v>
+        <v>0.5808547372361993</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001243594980252397</v>
+        <v>0.01060596000933934</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004291933691807168</v>
+        <v>0.5600674375964221</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0005828690534918262</v>
+        <v>0.6016420368759765</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1358913747251266</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.00321743951496409</v>
+        <v>0.002242891807688964</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00398389043383224</v>
+        <v>0.001173661517189244</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004590842253700753</v>
+        <v>-5.744249604259155e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01102572128362893</v>
+        <v>0.00454322611142052</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4193137172191295</v>
+        <v>0.0560018820898576</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002855410455972181</v>
+        <v>-0.001854532319157671</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001532410754135847</v>
+        <v>0.001243594980252399</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.002717928842030906</v>
+        <v>-0.004291933691807172</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003289010933225342</v>
+        <v>0.0005828690534918303</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8521824265148001</v>
+        <v>0.1358913747251274</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5808547372361993</v>
+        <v>0.003217439514964088</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01060596000933933</v>
+        <v>0.003983890433832258</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5600674375964221</v>
+        <v>-0.004590842253700789</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6016420368759765</v>
+        <v>0.01102572128362896</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.4193137172191319</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002242891807688962</v>
+        <v>0.0002855410455972202</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001173661517189244</v>
+        <v>0.001532410754135811</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.744249604259285e-05</v>
+        <v>-0.002717928842030832</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004543226111420517</v>
+        <v>0.003289010933225272</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05600188208985778</v>
+        <v>0.8521824265147957</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.427664644175297</v>
+        <v>-2.427664644175294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5181657220037946</v>
+        <v>0.5181657220038094</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509200555e-06</v>
+        <v>2.798063509202462e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763187</v>
+        <v>0.04283704187763178</v>
       </c>
       <c r="C3" t="n">
         <v>0.1065056610557123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.687533629353098</v>
+        <v>0.6875336293530989</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228887</v>
+        <v>0.3420089197228885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2258273108558932</v>
+        <v>0.225827310855893</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023923</v>
+        <v>0.1299064164023921</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7568550919253106</v>
+        <v>0.7568550919253108</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278904</v>
+        <v>0.1749116140278903</v>
       </c>
       <c r="D5" t="n">
-        <v>1.511047971683338e-05</v>
+        <v>1.511047971683312e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2420,7 +2420,7 @@
         <v>0.2139666880119048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3950624226561792</v>
+        <v>0.3950624226561794</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1330552971690138</v>
       </c>
       <c r="C7" t="n">
-        <v>0.195395281947656</v>
+        <v>0.1953952819476558</v>
       </c>
       <c r="D7" t="n">
-        <v>0.495900279135249</v>
+        <v>0.4959002791352487</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09728047689820801</v>
+        <v>-0.09728047689820793</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2107853049245229</v>
+        <v>0.2107853049245227</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6444295130162203</v>
+        <v>0.6444295130162204</v>
       </c>
     </row>
     <row r="9">
@@ -2468,7 +2468,7 @@
         <v>0.1704165076539108</v>
       </c>
       <c r="D9" t="n">
-        <v>3.584618716992673e-10</v>
+        <v>3.584618716992648e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131118</v>
+        <v>0.09164285114131061</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028381</v>
+        <v>0.2821462910028378</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093366</v>
+        <v>0.7453277880093379</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2093667135385769</v>
+        <v>0.2093667135385762</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685892</v>
+        <v>0.2718908402685897</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926253</v>
+        <v>0.4412764034926278</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2458167359844359</v>
+        <v>-0.2458167359844365</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060864204610709</v>
+        <v>0.3060864204610706</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4219193324752615</v>
+        <v>0.4219193324752599</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834365</v>
+        <v>0.2480605146834356</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653986</v>
+        <v>0.2698784026653987</v>
       </c>
       <c r="D13" t="n">
-        <v>0.358013668571723</v>
+        <v>0.3580136685717249</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666402</v>
+        <v>0.2887265920666393</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2797122646585147</v>
+        <v>0.2797122646585141</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3019657220075013</v>
+        <v>0.3019657220075017</v>
       </c>
     </row>
     <row r="15">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3364569693417747</v>
+        <v>0.336456969341774</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2683702941076246</v>
+        <v>0.268370294107624</v>
       </c>
       <c r="D15" t="n">
         <v>0.209949534738275</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.12123328197477</v>
+        <v>0.1212332819747693</v>
       </c>
       <c r="C16" t="n">
-        <v>0.267949350587075</v>
+        <v>0.2679493505870751</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758482</v>
+        <v>0.6509459134758502</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1766572982617274</v>
+        <v>0.1766572982617266</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752350890811207</v>
+        <v>0.27523508908112</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851416</v>
+        <v>0.5209761107851423</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578531</v>
+        <v>0.3813830960578522</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2677517444468913</v>
+        <v>0.2677517444468914</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1543334033865622</v>
+        <v>0.1543334033865632</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1210111614870004</v>
+        <v>0.1210111614869997</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204017</v>
+        <v>0.2775843004204014</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6628774877860026</v>
+        <v>0.6628774877860042</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2255181952666781</v>
+        <v>0.2255181952666772</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071247</v>
+        <v>0.2783783956071252</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4178747418803473</v>
+        <v>0.41787474188035</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2301319673853011</v>
+        <v>0.2301319673853003</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673309630216589</v>
+        <v>0.2673309630216584</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3893204404921197</v>
+        <v>0.3893204404921206</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04646654583854266</v>
+        <v>0.04646654583854196</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456553</v>
+        <v>0.2845286078456555</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8702738657351081</v>
+        <v>0.8702738657351102</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02162756752909017</v>
+        <v>-0.0216275675290909</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925905475884684</v>
+        <v>0.2925905475884689</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9410760153784391</v>
+        <v>0.9410760153784372</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8764973807420282</v>
+        <v>0.8764973807420284</v>
       </c>
       <c r="C24" t="n">
         <v>0.1598667289796821</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540285e-08</v>
+        <v>4.189413124540276e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5923085897232843</v>
+        <v>-0.5923085897232842</v>
       </c>
       <c r="C25" t="n">
         <v>0.116926282873278</v>
       </c>
       <c r="D25" t="n">
-        <v>4.069915021573901e-07</v>
+        <v>4.06991502157394e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1386000328216486</v>
+        <v>-0.1386000328216488</v>
       </c>
       <c r="C26" t="n">
         <v>0.1507698258117116</v>
       </c>
       <c r="D26" t="n">
-        <v>0.357947931392808</v>
+        <v>0.3579479313928077</v>
       </c>
     </row>
     <row r="27">
@@ -2756,7 +2756,7 @@
         <v>0.157443858905906</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5917334279738686</v>
+        <v>0.5917334279738685</v>
       </c>
     </row>
     <row r="28">
@@ -2769,10 +2769,10 @@
         <v>-0.1114085316198851</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483441008175725</v>
+        <v>0.1483441008175723</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4526440879579774</v>
+        <v>0.4526440879579769</v>
       </c>
     </row>
     <row r="29">
@@ -2782,93 +2782,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3220151818496276</v>
+        <v>-0.3220151818496277</v>
       </c>
       <c r="C29" t="n">
         <v>0.1549982402231347</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03775166539448375</v>
+        <v>0.03775166539448364</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002580638036074957</v>
+        <v>-0.0312074768090097</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007292353686099048</v>
+        <v>0.05994942728923066</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7234267695349467</v>
+        <v>0.6026709615967261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01847772081409666</v>
+        <v>0.01489842147412547</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0228622308980033</v>
+        <v>0.007094501199577966</v>
       </c>
       <c r="D31" t="n">
-        <v>0.418963730891023</v>
+        <v>0.03572922606502668</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01293860122823144</v>
+        <v>0.002580638036074951</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00818364581553413</v>
+        <v>0.007292353686099037</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1138708520154768</v>
+        <v>0.7234267695349468</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.03120747680900959</v>
+        <v>0.01847772081409665</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0599494272892295</v>
+        <v>0.02286223089800339</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6026709615967203</v>
+        <v>0.418963730891025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01489842147412546</v>
+        <v>-0.01293860122823149</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007094501199577954</v>
+        <v>0.008183645815534041</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03572922606502647</v>
+        <v>0.1138708520154716</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.015</v>
+        <v>-0.392</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>-0.027</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.015</v>
+        <v>0.365</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.001</v>
+        <v>-0.181</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.007</v>
+        <v>0.014</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.006</v>
+        <v>0.167</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.013</v>
+        <v>0.059</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.351</v>
+        <v>-0.007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.016</v>
+        <v>-0.028</v>
       </c>
       <c r="E9" t="n">
-        <v>0.335</v>
+        <v>-0.021</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.185</v>
+        <v>-0.215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.013</v>
+        <v>-0.058</v>
       </c>
       <c r="E10" t="n">
-        <v>0.172</v>
+        <v>0.157</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.007</v>
+        <v>-0.015</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.021</v>
+        <v>-0.015</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.181</v>
+        <v>-0.054</v>
       </c>
       <c r="D12" t="n">
-        <v>0.014</v>
+        <v>-0.023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.167</v>
+        <v>0.031</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.054</v>
+        <v>0.036</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.023</v>
+        <v>-0.001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.392</v>
+        <v>-0.001</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.027</v>
+        <v>-0.007</v>
       </c>
       <c r="E14" t="n">
-        <v>0.365</v>
+        <v>-0.006</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.006</v>
+        <v>0.025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.036</v>
+        <v>-0.001</v>
       </c>
       <c r="D16" t="n">
         <v>-0.001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.368</v>
+        <v>0.013</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.364</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.059</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.215</v>
+        <v>0.014</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.058</v>
+        <v>0.017</v>
       </c>
       <c r="E19" t="n">
-        <v>0.157</v>
+        <v>-0.003000000000000001</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.044</v>
+        <v>-0.095</v>
       </c>
       <c r="D20" t="n">
-        <v>0.027</v>
+        <v>0.005</v>
       </c>
       <c r="E20" t="n">
-        <v>0.017</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008</v>
+        <v>0.368</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.007</v>
+        <v>0.004</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001</v>
+        <v>0.364</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.076</v>
+        <v>-0.096</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E22" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.095</v>
+        <v>-0.012</v>
       </c>
       <c r="D23" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09</v>
+        <v>0.006</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.019</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.007</v>
+        <v>-0.029</v>
       </c>
       <c r="E24" t="n">
-        <v>0.012</v>
+        <v>0.061</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.096</v>
+        <v>-0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>0.017</v>
+        <v>-0.007</v>
       </c>
       <c r="E25" t="n">
-        <v>0.079</v>
+        <v>0.001</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01</v>
+        <v>-0.019</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.075</v>
+        <v>0.351</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.014</v>
+        <v>0.075</v>
       </c>
       <c r="D29" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="D30" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.012</v>
+        <v>0.185</v>
       </c>
       <c r="D31" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006</v>
+        <v>0.172</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.09</v>
+        <v>0.076</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.029</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.061</v>
+        <v>0.076</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9955799696542841</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1629543857601319</v>
+        <v>0.162954385760132</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836644</v>
+        <v>1.864929480836646</v>
       </c>
       <c r="F2" t="n">
         <v>1.150690388380934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713846</v>
+        <v>1.864005612713848</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.493998113457369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09154176342090867</v>
+        <v>0.09154176342090348</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071102</v>
+        <v>1.314579554071112</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843636</v>
+        <v>1.673416672843626</v>
       </c>
       <c r="F2" t="n">
-        <v>7.067206153166901e-60</v>
+        <v>7.067206153060451e-60</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01139734884641808</v>
+        <v>0.01139734884641803</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870615</v>
+        <v>0.01836912354870616</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661257</v>
+        <v>-0.02460547173661264</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04740016942944872</v>
+        <v>0.0474001694294487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931427</v>
+        <v>0.5349534598931449</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1517,13 +1517,13 @@
         <v>-0.09369904833157609</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04522288491293568</v>
+        <v>0.04522288491293567</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1823342740379298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005063822625222383</v>
+        <v>-0.005063822625222397</v>
       </c>
       <c r="F4" t="n">
         <v>0.03827115219154174</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152958</v>
+        <v>-0.01066467357152956</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981982333274044</v>
+        <v>0.02981982333274043</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06911045332904801</v>
+        <v>-0.06911045332904797</v>
       </c>
       <c r="E5" t="n">
         <v>0.04778110618598885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742431</v>
+        <v>0.7206149497742436</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04301492997829062</v>
+        <v>-0.04301492997829071</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03066350771200717</v>
+        <v>0.03066350771200716</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1031143007334909</v>
+        <v>-0.103114300733491</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690963</v>
+        <v>0.01708444077690954</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606749173778487</v>
+        <v>0.1606749173778477</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009581591331443436</v>
+        <v>0.0009581591331443962</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02954143714616892</v>
+        <v>0.0295414371461689</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05694199372490046</v>
+        <v>-0.05694199372490036</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05885831199118915</v>
+        <v>0.05885831199118916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875799</v>
+        <v>0.9741256203875784</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01499471859888912</v>
+        <v>-0.01499471859888913</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603005</v>
+        <v>0.03011722069603001</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07402338647755236</v>
+        <v>-0.07402338647755229</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977411</v>
+        <v>0.04403394927977403</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956141</v>
+        <v>0.6185696367956136</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619037</v>
+        <v>0.009760945713619091</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955249</v>
+        <v>0.02969887927955247</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0484477880555067</v>
+        <v>-0.04844778805550662</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274478</v>
+        <v>0.06796967948274481</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7424098394948977</v>
+        <v>0.7424098394948961</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057974</v>
+        <v>0.008945036718057849</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369309</v>
+        <v>0.05227344659369305</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09350903595335844</v>
+        <v>-0.09350903595335849</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1113991093894744</v>
+        <v>0.1113991093894742</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8641293418452034</v>
+        <v>0.8641293418452052</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07294946240716806</v>
+        <v>-0.072949462407168</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0495614724624486</v>
+        <v>0.04956147246244858</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.170088163454341</v>
+        <v>-0.1700881634543409</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02418923864000487</v>
+        <v>0.02418923864000488</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1410482591329777</v>
+        <v>0.1410482591329778</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08662342274371289</v>
+        <v>-0.08662342274371286</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05089844563154306</v>
+        <v>0.050898445631543</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1863825430506073</v>
+        <v>-0.1863825430506072</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318156</v>
+        <v>0.01313569756318146</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08877648025963114</v>
+        <v>0.08877648025963082</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.008024749836484041</v>
+        <v>-0.008024749836483986</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0511329505696972</v>
+        <v>0.05113295056969706</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1082434913763574</v>
+        <v>-0.1082434913763571</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09219399170338931</v>
+        <v>0.09219399170338909</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942478</v>
+        <v>0.8752929892942483</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04340557759080336</v>
+        <v>-0.04340557759080318</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05045929460802629</v>
+        <v>0.05045929460802626</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.142303977707831</v>
+        <v>-0.1423039777078308</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05549282252622432</v>
+        <v>0.05549282252622443</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082839</v>
+        <v>0.3896734268082854</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04574671530427658</v>
+        <v>-0.04574671530427654</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428281</v>
+        <v>0.04961392181428279</v>
       </c>
       <c r="D15" t="n">
         <v>-0.142988215192057</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350387</v>
+        <v>0.05149478458350386</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3565004068554809</v>
+        <v>0.356500406855481</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03713592023139944</v>
+        <v>-0.03713592023139937</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05010472347761168</v>
+        <v>0.05010472347761162</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1353393737028568</v>
+        <v>-0.1353393737028566</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06106753324005793</v>
+        <v>0.0610675332400579</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445322</v>
+        <v>0.4585927625445324</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01948239245873591</v>
+        <v>-0.01948239245873586</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05062347938805218</v>
+        <v>0.0506234793880521</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.118702588831424</v>
+        <v>-0.1187025888314237</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395213</v>
+        <v>0.07973780391395204</v>
       </c>
       <c r="F17" t="n">
-        <v>0.700349336416354</v>
+        <v>0.7003493364163544</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02897547644273362</v>
+        <v>-0.02897547644273353</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0510063081620003</v>
+        <v>0.05100630816200019</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289460034246056</v>
+        <v>-0.1289460034246053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913838</v>
+        <v>0.07099505053913825</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5699831381275133</v>
+        <v>0.5699831381275138</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04008864287509658</v>
+        <v>-0.04008864287509655</v>
       </c>
       <c r="C19" t="n">
         <v>0.04996256722766799</v>
@@ -1898,10 +1898,10 @@
         <v>-0.138013475216487</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0578361894662939</v>
+        <v>0.05783618946629392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4223369033872225</v>
+        <v>0.4223369033872229</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662674</v>
+        <v>-0.08980962914662668</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04956030606584797</v>
+        <v>0.04956030606584801</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1869460440984707</v>
+        <v>-0.1869460440984708</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007326785805217256</v>
+        <v>0.007326785805217395</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0699663870864064</v>
+        <v>0.06996638708640684</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943052</v>
+        <v>0.003397924751943098</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773255</v>
+        <v>0.04891083189773248</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09246554422150562</v>
+        <v>-0.09246554422150542</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09926139372539171</v>
+        <v>0.09926139372539163</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446140588838088</v>
+        <v>0.944614058883808</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.005820590202436491</v>
+        <v>-0.00582059020243632</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04992222605418416</v>
+        <v>0.04992222605418412</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967046</v>
+        <v>-0.1036663552967043</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0920251748918316</v>
+        <v>0.09202517489183169</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9071824564981807</v>
+        <v>0.9071824564981834</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06091882540351701</v>
+        <v>-0.06091882540351698</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04983273321557469</v>
+        <v>0.04983273321557472</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1585891877572363</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020227</v>
+        <v>0.03675153695020235</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215314283124583</v>
+        <v>0.2215314283124588</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884725</v>
+        <v>-0.04546552218884722</v>
       </c>
       <c r="C24" t="n">
         <v>0.04088368473780891</v>
@@ -2023,10 +2023,10 @@
         <v>-0.1255960718302426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0346650274525481</v>
+        <v>0.03466502745254811</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958384</v>
+        <v>0.2661080237958385</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005855003749821487</v>
+        <v>0.0058550037498215</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273565</v>
+        <v>0.02357096913273562</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0403432468310457</v>
+        <v>-0.04034324683104562</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05205325433068868</v>
+        <v>0.05205325433068862</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625448</v>
+        <v>0.8038257535625442</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02022035479316629</v>
+        <v>0.02022035479316614</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847209635064418</v>
+        <v>0.02847209635064417</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845061</v>
+        <v>-0.03558392861845072</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07602463820478318</v>
+        <v>0.07602463820478302</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4775916198870058</v>
+        <v>0.4775916198870087</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390033</v>
+        <v>0.01017504924390034</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920817082181941</v>
+        <v>0.02920817082181939</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115939</v>
+        <v>-0.04707191362115933</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210896005</v>
+        <v>0.06742201210896001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194186</v>
+        <v>0.7275675029194182</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0307527429121369</v>
+        <v>0.03075274291213691</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02852520938942747</v>
+        <v>0.02852520938942743</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02515564014260473</v>
+        <v>-0.02515564014260465</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687854</v>
+        <v>0.08666112596687847</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2809935950997029</v>
+        <v>0.2809935950997021</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2142,16 +2142,16 @@
         <v>-0.0143177518740259</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140895</v>
+        <v>0.02757795020140893</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622657</v>
+        <v>-0.06836954103622653</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817476</v>
+        <v>0.03973403728817473</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206333</v>
+        <v>0.6036394802206331</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2167,16 +2167,16 @@
         <v>0.3642249454799705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03859338896492541</v>
+        <v>0.03859338896492542</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2885832930673712</v>
+        <v>0.2885832930673711</v>
       </c>
       <c r="E30" t="n">
         <v>0.4398665978925699</v>
       </c>
       <c r="F30" t="n">
-        <v>3.817947647451369e-21</v>
+        <v>3.817947647451479e-21</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5808547372361993</v>
+        <v>-0.001854532319157672</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01060596000933939</v>
+        <v>0.001243594980252395</v>
       </c>
       <c r="D31" t="n">
-        <v>0.560067437596422</v>
+        <v>-0.004291933691807166</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6016420368759766</v>
+        <v>0.000582869053491822</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1358913747251261</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001854532319157671</v>
+        <v>0.5808547372361993</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001243594980252397</v>
+        <v>0.01060596000933936</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004291933691807169</v>
+        <v>0.5600674375964221</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0005828690534918264</v>
+        <v>0.6016420368759765</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1358913747251267</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002855410455972195</v>
+        <v>0.0002855410455972233</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001532410754135868</v>
+        <v>0.001532410754135825</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.002717928842030945</v>
+        <v>-0.002717928842030857</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003289010933225384</v>
+        <v>0.003289010933225304</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8521824265148015</v>
+        <v>0.8521824265147955</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.003217439514964092</v>
+        <v>0.003217439514964091</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003983890433832266</v>
+        <v>0.003983890433832272</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004590842253700801</v>
+        <v>-0.004590842253700812</v>
       </c>
       <c r="E34" t="n">
         <v>0.01102572128362899</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4193137172191322</v>
+        <v>0.4193137172191329</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002242891807688964</v>
+        <v>0.002242891807688965</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001173661517189242</v>
+        <v>0.001173661517189241</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.744249604258808e-05</v>
+        <v>-5.744249604258504e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004543226111420516</v>
+        <v>0.004543226111420514</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05600188208985725</v>
+        <v>0.05600188208985693</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.427664644175297</v>
+        <v>-2.427664644175294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5181657220038028</v>
+        <v>0.5181657220038156</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509201582e-06</v>
+        <v>2.798063509203218e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763192</v>
+        <v>0.04283704187763185</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065056610557123</v>
+        <v>0.1065056610557124</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6875336293530978</v>
+        <v>0.6875336293530986</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228887</v>
+        <v>0.3420089197228885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2258273108558931</v>
+        <v>0.2258273108558932</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023923</v>
+        <v>0.1299064164023925</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7568550919253106</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278902</v>
+        <v>0.1749116140278904</v>
       </c>
       <c r="D5" t="n">
-        <v>1.511047971683288e-05</v>
+        <v>1.511047971683326e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1819727920118004</v>
+        <v>-0.1819727920118002</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2139666880119048</v>
+        <v>0.2139666880119049</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3950624226561785</v>
+        <v>0.3950624226561791</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1330552971690138</v>
+        <v>0.1330552971690139</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1953952819476561</v>
+        <v>0.195395281947656</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4959002791352496</v>
+        <v>0.4959002791352488</v>
       </c>
     </row>
     <row r="8">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09728047689820803</v>
+        <v>-0.097280476898208</v>
       </c>
       <c r="C8" t="n">
         <v>0.2107853049245229</v>
@@ -2465,10 +2465,10 @@
         <v>1.068702246714659</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1704165076539109</v>
+        <v>0.1704165076539107</v>
       </c>
       <c r="D9" t="n">
-        <v>3.584618716992699e-10</v>
+        <v>3.584618716992556e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131082</v>
+        <v>0.09164285114131052</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028381</v>
+        <v>0.2821462910028385</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093375</v>
+        <v>0.7453277880093387</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2093667135385765</v>
+        <v>0.209366713538576</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685894</v>
+        <v>0.2718908402685897</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926265</v>
+        <v>0.4412764034926281</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2458167359844362</v>
+        <v>-0.2458167359844367</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060864204610709</v>
+        <v>0.3060864204610716</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4219193324752608</v>
+        <v>0.421919332475261</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834359</v>
+        <v>0.2480605146834355</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653986</v>
+        <v>0.2698784026653991</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3580136685717242</v>
+        <v>0.358013668571726</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666398</v>
+        <v>0.2887265920666393</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2797122646585147</v>
+        <v>0.279712264658515</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3019657220075019</v>
+        <v>0.3019657220075033</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3364569693417743</v>
+        <v>0.336456969341774</v>
       </c>
       <c r="C15" t="n">
-        <v>0.268370294107624</v>
+        <v>0.2683702941076243</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2099495347382745</v>
+        <v>0.2099495347382754</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1212332819747696</v>
+        <v>0.1212332819747691</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2679493505870748</v>
+        <v>0.2679493505870756</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758488</v>
+        <v>0.6509459134758514</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1766572982617269</v>
+        <v>0.1766572982617265</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752350890811202</v>
+        <v>0.2752350890811209</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851418</v>
+        <v>0.5209761107851441</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578525</v>
+        <v>0.3813830960578519</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2677517444468916</v>
+        <v>0.2677517444468921</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1543334033865632</v>
+        <v>0.1543334033865648</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1210111614870001</v>
+        <v>0.1210111614869995</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204012</v>
+        <v>0.2775843004204018</v>
       </c>
       <c r="D19" t="n">
-        <v>0.662877487786003</v>
+        <v>0.6628774877860051</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2255181952666776</v>
+        <v>0.225518195266677</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071247</v>
+        <v>0.2783783956071257</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4178747418803483</v>
+        <v>0.4178747418803513</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2301319673853007</v>
+        <v>0.2301319673853001</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673309630216584</v>
+        <v>0.2673309630216597</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3893204404921196</v>
+        <v>0.389320440492123</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04646654583854237</v>
+        <v>0.04646654583854187</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456554</v>
+        <v>0.2845286078456556</v>
       </c>
       <c r="D22" t="n">
-        <v>0.870273865735109</v>
+        <v>0.8702738657351106</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02162756752909064</v>
+        <v>-0.0216275675290911</v>
       </c>
       <c r="C23" t="n">
-        <v>0.292590547588468</v>
+        <v>0.2925905475884691</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9410760153784377</v>
+        <v>0.9410760153784367</v>
       </c>
     </row>
     <row r="24">
@@ -2705,10 +2705,10 @@
         <v>0.8764973807420283</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1598667289796822</v>
+        <v>0.1598667289796821</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540331e-08</v>
+        <v>4.189413124540285e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5923085897232843</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169262828732779</v>
+        <v>0.1169262828732781</v>
       </c>
       <c r="D25" t="n">
-        <v>4.069915021573848e-07</v>
+        <v>4.069915021574022e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2740,7 +2740,7 @@
         <v>0.1507698258117116</v>
       </c>
       <c r="D26" t="n">
-        <v>0.357947931392807</v>
+        <v>0.3579479313928068</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08444119781568341</v>
+        <v>-0.08444119781568356</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1574438589059061</v>
+        <v>0.157443858905906</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5917334279738689</v>
+        <v>0.591733427973868</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1114085316198851</v>
+        <v>-0.1114085316198852</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483441008175724</v>
+        <v>0.1483441008175725</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4526440879579769</v>
+        <v>0.4526440879579768</v>
       </c>
     </row>
     <row r="29">
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3220151818496277</v>
+        <v>-0.3220151818496279</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1549982402231345</v>
+        <v>0.1549982402231347</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0377516653944835</v>
+        <v>0.03775166539448363</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.03120747680900965</v>
+        <v>0.002580638036074954</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0599494272892301</v>
+        <v>0.007292353686099036</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6026709615967234</v>
+        <v>0.7234267695349466</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002580638036074952</v>
+        <v>-0.03120747680900965</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007292353686099041</v>
+        <v>0.05994942728923073</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7234267695349469</v>
+        <v>0.6026709615967271</v>
       </c>
     </row>
     <row r="32">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01293860122823144</v>
+        <v>-0.01293860122823147</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008183645815534393</v>
+        <v>0.008183645815534327</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1138708520154885</v>
+        <v>0.1138708520154848</v>
       </c>
     </row>
     <row r="33">
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01847772081409668</v>
+        <v>0.01847772081409663</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02286223089800329</v>
+        <v>0.02286223089800341</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4189637308910223</v>
+        <v>0.418963730891026</v>
       </c>
     </row>
     <row r="34">
@@ -2865,10 +2865,10 @@
         <v>0.01489842147412546</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007094501199577965</v>
+        <v>0.007094501199577966</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03572922606502674</v>
+        <v>0.03572922606502676</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.181</v>
+        <v>-0.392</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="E6" t="n">
-        <v>0.172</v>
+        <v>0.361</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01</v>
+        <v>-0.181</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005</v>
+        <v>0.172</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.076</v>
+        <v>0.044</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="E8" t="n">
-        <v>0.076</v>
+        <v>0.018</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.095</v>
+        <v>0.351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.093</v>
+        <v>0.335</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.008</v>
+        <v>0.014</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>-0.007000000000000001</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.392</v>
+        <v>-0.095</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.031</v>
+        <v>0.002</v>
       </c>
       <c r="E11" t="n">
-        <v>0.361</v>
+        <v>0.093</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.001</v>
+        <v>-0.215</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003</v>
+        <v>-0.063</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.002</v>
+        <v>0.152</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="D13" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.007000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="D14" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.045</v>
+        <v>0.076</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.033</v>
+        <v>0.368</v>
       </c>
       <c r="D15" t="n">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="E15" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.363</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="D16" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E16" t="n">
         <v>-0.002</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.005</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.036</v>
+        <v>-0.001</v>
       </c>
       <c r="D17" t="n">
         <v>-0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.032</v>
+        <v>-0.003</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.015</v>
+        <v>0.013</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.028</v>
+        <v>0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.096</v>
+        <v>0.007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.021</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.075</v>
+        <v>0.005</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.001</v>
+        <v>-0.054</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.004</v>
+        <v>-0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.003</v>
+        <v>0.034</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.028</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.021</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.075</v>
+        <v>0.185</v>
       </c>
       <c r="D22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="E22" t="n">
-        <v>0.066</v>
+        <v>0.167</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.019</v>
+        <v>0.059</v>
       </c>
       <c r="D23" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="E23" t="n">
-        <v>0.014</v>
+        <v>0.045</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.351</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.016</v>
+        <v>-0.029</v>
       </c>
       <c r="E24" t="n">
-        <v>0.335</v>
+        <v>0.061</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.033</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02</v>
+        <v>0.024</v>
       </c>
       <c r="E25" t="n">
-        <v>0.034</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.09</v>
+        <v>0.036</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.029</v>
+        <v>-0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>0.061</v>
+        <v>0.032</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.368</v>
+        <v>0.075</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.363</v>
+        <v>0.066</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.013</v>
+        <v>-0.019</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.215</v>
+        <v>-0.015</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.063</v>
+        <v>-0.028</v>
       </c>
       <c r="E30" t="n">
-        <v>0.152</v>
+        <v>-0.013</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.185</v>
+        <v>-0.096</v>
       </c>
       <c r="D31" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="E31" t="n">
-        <v>0.167</v>
+        <v>0.075</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.044</v>
+        <v>-0.007</v>
       </c>
       <c r="D32" t="n">
-        <v>0.026</v>
+        <v>-0.028</v>
       </c>
       <c r="E32" t="n">
-        <v>0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>0.9950246761341104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1609838789597045</v>
+        <v>0.1609838789597046</v>
       </c>
       <c r="E2" t="n">
         <v>1.82043870212157</v>
@@ -1403,7 +1403,7 @@
         <v>1.151957513402452</v>
       </c>
       <c r="G2" t="n">
-        <v>1.820173420053883</v>
+        <v>1.820173420053884</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.480396945623569</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0923135560579946</v>
+        <v>0.09231355605799561</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29946570046508</v>
+        <v>1.299465700465078</v>
       </c>
       <c r="E2" t="n">
-        <v>1.661328190782057</v>
+        <v>1.66132819078206</v>
       </c>
       <c r="F2" t="n">
-        <v>7.091592649192629e-58</v>
+        <v>7.091592649212459e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,13 +1492,13 @@
         <v>0.01014980283236199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836499278683017</v>
+        <v>0.01836499278683015</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02584492160616302</v>
+        <v>-0.02584492160616299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04614452727088701</v>
+        <v>0.04614452727088696</v>
       </c>
       <c r="F3" t="n">
         <v>0.5804885690891299</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09487871714183246</v>
+        <v>-0.09487871714183245</v>
       </c>
       <c r="C4" t="n">
         <v>0.04520079875316899</v>
@@ -1523,10 +1523,10 @@
         <v>-0.1834706547704867</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.00628677951317827</v>
+        <v>-0.006286779513178242</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03581253134930478</v>
+        <v>0.03581253134930484</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01205799529998014</v>
+        <v>-0.01205799529998015</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981223863521451</v>
+        <v>0.02981223863521449</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07048890932351411</v>
+        <v>-0.07048890932351409</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04637291872355383</v>
+        <v>0.04637291872355379</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6858711013557706</v>
+        <v>0.6858711013557701</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1567,16 +1567,16 @@
         <v>-0.04304972157863009</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03059882979701846</v>
+        <v>0.03059882979701848</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1030223259498573</v>
+        <v>-0.1030223259498574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01692288279259715</v>
+        <v>0.01692288279259718</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1594548344009052</v>
+        <v>0.1594548344009056</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001240700728441063</v>
+        <v>0.001240700728441044</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0294679635986441</v>
+        <v>0.02946796359864412</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05651544662263869</v>
+        <v>-0.05651544662263876</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05899684807952081</v>
+        <v>0.05899684807952085</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9664162895200011</v>
+        <v>0.9664162895200017</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01496662172759922</v>
+        <v>-0.01496662172759925</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03016435277694362</v>
+        <v>0.03016435277694363</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07408766678736949</v>
+        <v>-0.07408766678736953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04415442333217104</v>
+        <v>0.04415442333217102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6197750642373498</v>
+        <v>0.6197750642373493</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01054368268372455</v>
+        <v>0.01054368268372452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02965183417955851</v>
+        <v>0.02965183417955853</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04757284438376392</v>
+        <v>-0.04757284438376398</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06866020975121301</v>
+        <v>0.06866020975121304</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7221530148300351</v>
+        <v>0.7221530148300359</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008469138305614014</v>
+        <v>0.008469138305613943</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05226807550480057</v>
+        <v>0.0522680755048006</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09397440722501532</v>
+        <v>-0.09397440722501545</v>
       </c>
       <c r="E10" t="n">
         <v>0.1109126838362433</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8712800895636489</v>
+        <v>0.87128008956365</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07442515093376462</v>
+        <v>-0.07442515093376466</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04961328479180979</v>
+        <v>0.04961328479180981</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1716654022804406</v>
+        <v>-0.1716654022804407</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02281510041291136</v>
+        <v>0.02281510041291135</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1335871310677167</v>
+        <v>0.1335871310677165</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08771751346518671</v>
+        <v>-0.08771751346518676</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05098868776485559</v>
+        <v>0.05098868776485564</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1876535051032618</v>
+        <v>-0.1876535051032619</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01221847817288835</v>
+        <v>0.0122184781728884</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08537195926819326</v>
+        <v>0.08537195926819338</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.01112220983087749</v>
+        <v>-0.0111222098308775</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05102736916981043</v>
+        <v>0.0510273691698105</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1111340156295354</v>
+        <v>-0.1111340156295356</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08888959596778047</v>
+        <v>0.08888959596778061</v>
       </c>
       <c r="F13" t="n">
         <v>0.827455934193412</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04293550244653974</v>
+        <v>-0.0429355024465398</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05055059599645621</v>
+        <v>0.05055059599645623</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1420128499966286</v>
+        <v>-0.1420128499966287</v>
       </c>
       <c r="E14" t="n">
         <v>0.05614184510354906</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3956826737847416</v>
+        <v>0.3956826737847413</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.044376478746274</v>
+        <v>-0.04437647874627407</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04933346508523263</v>
+        <v>0.0493334650852327</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1410682935458942</v>
+        <v>-0.1410682935458944</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05231533605334619</v>
+        <v>0.05231533605334626</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3683753135199095</v>
+        <v>0.3683753135199094</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03724912566851705</v>
+        <v>-0.03724912566851709</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0501333524597545</v>
+        <v>0.05013335245975453</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1355086909138884</v>
+        <v>-0.1355086909138885</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06101043957685429</v>
+        <v>0.06101043957685431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4574811395184715</v>
+        <v>0.4574811395184714</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.02013564391904809</v>
+        <v>-0.02013564391904812</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05067591738089412</v>
+        <v>0.05067591738089416</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1194586168691279</v>
+        <v>-0.119458616869128</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07918732903103175</v>
+        <v>0.07918732903103178</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6911156643997002</v>
+        <v>0.6911156643996998</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02951065520775305</v>
+        <v>-0.02951065520775304</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05110457249157436</v>
+        <v>0.05110457249157446</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1296737767365552</v>
+        <v>-0.1296737767365553</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07065246632104907</v>
+        <v>0.07065246632104925</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5636312794271754</v>
+        <v>0.5636312794271764</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04054326933592469</v>
+        <v>-0.04054326933592471</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05001967309932245</v>
+        <v>0.05001967309932249</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1385800271290637</v>
+        <v>-0.1385800271290638</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05749348845721428</v>
+        <v>0.05749348845721435</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4176261697368353</v>
+        <v>0.4176261697368354</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.09100057242621593</v>
+        <v>-0.09100057242621594</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04944530324025027</v>
+        <v>0.04944530324025028</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1879115859817681</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005910441129336239</v>
+        <v>0.005910441129336252</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06570527191995243</v>
+        <v>0.06570527191995246</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.00369568530611819</v>
+        <v>0.00369568530611814</v>
       </c>
       <c r="C21" t="n">
         <v>0.04898316444458103</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09230955285406356</v>
+        <v>-0.09230955285406361</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09970092346629994</v>
+        <v>0.09970092346629988</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9398582124386513</v>
+        <v>0.9398582124386522</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006269093317233029</v>
+        <v>-0.006269093317233094</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05001575119043809</v>
+        <v>0.05001575119043807</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.104298164310208</v>
+        <v>-0.1042981643102081</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09175997767574195</v>
+        <v>0.09175997767574187</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9002525019265126</v>
+        <v>0.9002525019265116</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06082558774950664</v>
+        <v>-0.06082558774950667</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04992592593427266</v>
+        <v>0.04992592593427267</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1586786044754953</v>
+        <v>-0.1586786044754954</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03702742897648204</v>
+        <v>0.03702742897648202</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2231036582797601</v>
+        <v>0.22310365827976</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04566521685749294</v>
+        <v>-0.0456652168574929</v>
       </c>
       <c r="C24" t="n">
         <v>0.0409915365619473</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1260071521898665</v>
+        <v>-0.1260071521898664</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03467671847488061</v>
+        <v>0.03467671847488064</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2652724350207529</v>
+        <v>0.2652724350207532</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005875090878894528</v>
+        <v>0.00587509087889457</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02360333061262573</v>
+        <v>0.02360333061262574</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04038658703704364</v>
+        <v>-0.04038658703704361</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05213676879483269</v>
+        <v>0.05213676879483275</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8034308633569947</v>
+        <v>0.8034308633569933</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01971342777812012</v>
+        <v>0.01971342777812008</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02844465885270394</v>
+        <v>0.02844465885270396</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03603707912570801</v>
+        <v>-0.03603707912570811</v>
       </c>
       <c r="E26" t="n">
         <v>0.07546393468194826</v>
       </c>
       <c r="F26" t="n">
-        <v>0.48828132975465</v>
+        <v>0.4882813297546514</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.009295584463230852</v>
+        <v>0.009295584463230843</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02918964367861766</v>
+        <v>0.02918964367861768</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04791506586841703</v>
+        <v>-0.04791506586841706</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06650623479487873</v>
+        <v>0.06650623479487874</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7501399152983234</v>
+        <v>0.7501399152983237</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02910093430210231</v>
+        <v>0.0291009343021023</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02854626163111396</v>
+        <v>0.02854626163111398</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02684871038813868</v>
+        <v>-0.02684871038813871</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08505057899234329</v>
+        <v>0.08505057899234331</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3079985571095429</v>
+        <v>0.3079985571095434</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01455084235275102</v>
+        <v>-0.01455084235275106</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02750445917332441</v>
+        <v>0.02750445917332445</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06845859174671917</v>
+        <v>-0.06845859174671928</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03935690704121713</v>
+        <v>0.03935690704121717</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5967806460697769</v>
+        <v>0.5967806460697764</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2472871475932631</v>
+        <v>0.2472871475932633</v>
       </c>
       <c r="C30" t="n">
-        <v>0.120490624298827</v>
+        <v>0.1204906242988269</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01112986349281544</v>
+        <v>0.01112986349281583</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4834444316937109</v>
+        <v>0.4834444316937108</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04013709890141712</v>
+        <v>0.04013709890141682</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>big_span</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002290121492346934</v>
+        <v>0.002980661163500458</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001172016575419001</v>
+        <v>0.03141225726931023</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.988784758279066e-06</v>
+        <v>-0.0585862317574541</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004587231769452147</v>
+        <v>0.06454755408445502</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0507011057916955</v>
+        <v>0.9244034114648536</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.000295941259900692</v>
+        <v>0.58046395480427</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001533727514455641</v>
+        <v>0.01059206443188444</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.002710109430530498</v>
+        <v>0.5597038899958489</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003301991950331883</v>
+        <v>0.6012240196126912</v>
       </c>
       <c r="F32" t="n">
-        <v>0.846993767631772</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.58046395480427</v>
+        <v>0.002290121492346935</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0105920644318845</v>
+        <v>0.001172016575419001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5597038899958487</v>
+        <v>-6.988784758278632e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6012240196126913</v>
+        <v>0.004587231769452148</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.05070110579169546</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>big_span_treatment</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1348384925790881</v>
+        <v>0.0002959412599006877</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1244165069175249</v>
+        <v>0.001533727514455618</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1090133800615393</v>
+        <v>-0.002710109430530459</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3786903652197154</v>
+        <v>0.003301991950331835</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2784681626532741</v>
+        <v>0.846993767631772</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>big_span</t>
+          <t>big_span_treatment</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002980661163500418</v>
+        <v>0.134838492579088</v>
       </c>
       <c r="C35" t="n">
-        <v>0.03141225726931016</v>
+        <v>0.1244165069175251</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.058586231757454</v>
+        <v>-0.1090133800615397</v>
       </c>
       <c r="E35" t="n">
-        <v>0.06454755408445484</v>
+        <v>0.3786903652197156</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9244034114648544</v>
+        <v>0.278468162653275</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2314,19 +2314,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0007527623898864668</v>
+        <v>0.0007527623898864515</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004069278319009156</v>
+        <v>0.004069278319009195</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.007222876558441172</v>
+        <v>-0.007222876558441263</v>
       </c>
       <c r="E36" t="n">
-        <v>0.008728401338214106</v>
+        <v>0.008728401338214167</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8532394631073704</v>
+        <v>0.8532394631073748</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2378,10 +2378,10 @@
         <v>-2.305476704343799</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5231558886398957</v>
+        <v>0.5231558886399189</v>
       </c>
       <c r="D2" t="n">
-        <v>1.048781286690859e-05</v>
+        <v>1.048781286691801e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04353420434069191</v>
+        <v>0.04353420434069196</v>
       </c>
       <c r="C3" t="n">
-        <v>0.106409056742103</v>
+        <v>0.1064090567421032</v>
       </c>
       <c r="D3" t="n">
         <v>0.6824506959222996</v>
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3432925190833495</v>
+        <v>0.3432925190833494</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2255266975590037</v>
+        <v>0.2255266975590038</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1279636622422186</v>
+        <v>0.1279636622422188</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.7605144812869579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749746302893661</v>
+        <v>0.1749746302893667</v>
       </c>
       <c r="D5" t="n">
-        <v>1.383729881436048e-05</v>
+        <v>1.383729881436144e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2442,10 +2442,10 @@
         <v>-0.1847253344570327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2137839199842164</v>
+        <v>0.2137839199842169</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3875467073943133</v>
+        <v>0.3875467073943144</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1315557084716397</v>
+        <v>0.1315557084716396</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1954900602479314</v>
+        <v>0.1954900602479319</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5009769126453631</v>
+        <v>0.5009769126453645</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09701217403726656</v>
+        <v>-0.09701217403726664</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2106651209791175</v>
+        <v>0.210665120979118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6451543539935694</v>
+        <v>0.6451543539935698</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>1.06836372423693</v>
       </c>
       <c r="C9" t="n">
-        <v>0.17039906365261</v>
+        <v>0.1703990636526104</v>
       </c>
       <c r="D9" t="n">
-        <v>3.615710772054429e-10</v>
+        <v>3.615710772054783e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08689152366058274</v>
+        <v>0.08689152366058303</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2814998287132306</v>
+        <v>0.2814998287132319</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7575699410849728</v>
+        <v>0.7575699410849731</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.201795137724893</v>
+        <v>0.2017951377248935</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2720725433902599</v>
+        <v>0.2720725433902608</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4582714980348429</v>
+        <v>0.4582714980348432</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.254717913624369</v>
+        <v>-0.2547179136243685</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3064456171059297</v>
+        <v>0.3064456171059304</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4058600711263241</v>
+        <v>0.4058600711263259</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2464230505728121</v>
+        <v>0.2464230505728126</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698278039491651</v>
+        <v>0.2698278039491653</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3611055994101838</v>
+        <v>0.3611055994101833</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2748558804119319</v>
+        <v>0.2748558804119323</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2804187360263206</v>
+        <v>0.2804187360263232</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3270059980902326</v>
+        <v>0.3270059980902364</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.332378742824722</v>
+        <v>0.3323787428247227</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2680469343907508</v>
+        <v>0.268046934390752</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2149746432427817</v>
+        <v>0.2149746432427828</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1140118957648396</v>
+        <v>0.1140118957648401</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2676707923199497</v>
+        <v>0.2676707923199509</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6701510266435819</v>
+        <v>0.6701510266435817</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1677017081805965</v>
+        <v>0.1677017081805971</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2756856221796299</v>
+        <v>0.2756856221796307</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5429833635124652</v>
+        <v>0.5429833635124649</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3735057320986759</v>
+        <v>0.3735057320986765</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2682143805306411</v>
+        <v>0.2682143805306412</v>
       </c>
       <c r="D18" t="n">
-        <v>0.163751628838233</v>
+        <v>0.1637516288382325</v>
       </c>
     </row>
     <row r="19">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.113216954125305</v>
+        <v>0.1132169541253054</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2774495710571204</v>
+        <v>0.2774495710571215</v>
       </c>
       <c r="D19" t="n">
         <v>0.6832272913858297</v>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2221611794684661</v>
+        <v>0.2221611794684668</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2786852004816445</v>
+        <v>0.2786852004816464</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4253487681357134</v>
+        <v>0.4253487681357151</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2186935943615167</v>
+        <v>0.2186935943615172</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2670399544657338</v>
+        <v>0.2670399544657355</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4128123266990043</v>
+        <v>0.4128123266990062</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03623470789752637</v>
+        <v>0.03623470789752706</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2843907115968459</v>
+        <v>0.2843907115968473</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8986145456843156</v>
+        <v>0.8986145456843142</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02820713606357468</v>
+        <v>-0.02820713606357417</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2921362658986943</v>
+        <v>0.2921362658986958</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9230800146895277</v>
+        <v>0.9230800146895295</v>
       </c>
     </row>
     <row r="24">
@@ -2733,7 +2733,7 @@
         <v>0.159855830901508</v>
       </c>
       <c r="D24" t="n">
-        <v>4.088004552582568e-08</v>
+        <v>4.088004552582586e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5917569512165407</v>
+        <v>-0.5917569512165406</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1170694015370462</v>
+        <v>0.1170694015370464</v>
       </c>
       <c r="D25" t="n">
-        <v>4.309473117540662e-07</v>
+        <v>4.30947311754086e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1379347416692539</v>
+        <v>-0.1379347416692537</v>
       </c>
       <c r="C26" t="n">
-        <v>0.150758529596044</v>
+        <v>0.1507585295960442</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3602240607133723</v>
+        <v>0.360224060713374</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08351770317020622</v>
+        <v>-0.08351770317020611</v>
       </c>
       <c r="C27" t="n">
         <v>0.1575153679928091</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5959598250856347</v>
+        <v>0.5959598250856352</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1104442107318848</v>
+        <v>-0.1104442107318846</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1485662159865757</v>
+        <v>0.148566215986576</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4572391948936894</v>
+        <v>0.4572391948936911</v>
       </c>
     </row>
     <row r="29">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3186105264926382</v>
+        <v>-0.318610526492638</v>
       </c>
       <c r="C29" t="n">
         <v>0.1550508799957422</v>
@@ -2819,65 +2819,65 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>big_span</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01482976190572093</v>
+        <v>-0.1816898713049951</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007101299600452754</v>
+        <v>0.1675437923427983</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03676928414705771</v>
+        <v>0.2781732450178475</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01307736032002064</v>
+        <v>-0.03170385269830844</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008192979711924422</v>
+        <v>0.06006853305094995</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1104516092929849</v>
+        <v>0.5976418440010126</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.03170385269830843</v>
+        <v>0.01482976190572093</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06006853305094961</v>
+        <v>0.007101299600452767</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5976418440010105</v>
+        <v>0.03676928414705806</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>big_span</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.181689871304995</v>
+        <v>-0.01307736032002064</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1675437923427971</v>
+        <v>0.008192979711924618</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2781732450178442</v>
+        <v>0.1104516092929934</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03008506166450894</v>
+        <v>0.03008506166450895</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02331722086972509</v>
+        <v>0.02331722086972511</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1969636114055594</v>
+        <v>0.1969636114055597</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.024</v>
+        <v>-0.082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004</v>
+        <v>-0.027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.369</v>
+        <v>0.045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.362</v>
+        <v>0.039</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.388</v>
+        <v>-0.008</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.031</v>
+        <v>-0.021</v>
       </c>
       <c r="E8" t="n">
-        <v>0.357</v>
+        <v>-0.013</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003</v>
+        <v>-0.031</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003</v>
+        <v>0.026</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.036</v>
+        <v>-0.117</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03</v>
+        <v>0.114</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.095</v>
+        <v>0.19</v>
       </c>
       <c r="D11" t="n">
-        <v>0.015</v>
+        <v>0.024</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08</v>
+        <v>0.166</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008</v>
+        <v>-0.183</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003</v>
+        <v>0.174</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.082</v>
+        <v>0.011</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.027</v>
+        <v>0.004</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="D14" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="E14" t="n">
-        <v>0.011</v>
+        <v>0.03</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.183</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.174</v>
+        <v>0.003</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.216</v>
+        <v>0.075</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>0.008</v>
       </c>
       <c r="E16" t="n">
-        <v>0.156</v>
+        <v>0.067</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="E18" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.015</v>
+        <v>0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.024</v>
+        <v>0.005</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.117</v>
+        <v>0.35</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.003</v>
+        <v>0.019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.114</v>
+        <v>0.331</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.045</v>
+        <v>0.369</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.039</v>
+        <v>0.362</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>-0.388</v>
+      </c>
+      <c r="D23" t="n">
         <v>-0.031</v>
       </c>
-      <c r="D23" t="n">
-        <v>-0.005</v>
-      </c>
       <c r="E23" t="n">
-        <v>0.026</v>
+        <v>0.357</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.075</v>
+        <v>-0.015</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.067</v>
+        <v>0.013</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.216</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.021</v>
+        <v>-0.06</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.013</v>
+        <v>0.156</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.099</v>
+        <v>0.024</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002</v>
+        <v>0.024</v>
       </c>
       <c r="E27" t="n">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.19</v>
+        <v>0.036</v>
       </c>
       <c r="D28" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="E28" t="n">
-        <v>0.166</v>
+        <v>0.016</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>0.006</v>
+        <v>-0.024</v>
       </c>
       <c r="E29" t="n">
-        <v>0.012</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.35</v>
+        <v>0.099</v>
       </c>
       <c r="D30" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.331</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="D31" t="n">
         <v>0.015</v>
       </c>
-      <c r="D31" t="n">
-        <v>0.019</v>
-      </c>
       <c r="E31" t="n">
-        <v>-0.004</v>
+        <v>0.08</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="E32" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9949908017929653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1657439023898879</v>
+        <v>0.165743902389888</v>
       </c>
       <c r="E2" t="n">
-        <v>1.853163385476146</v>
+        <v>1.853163385476147</v>
       </c>
       <c r="F2" t="n">
         <v>1.168712646832276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.851455159122648</v>
+        <v>1.851455159122649</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.43091629243017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1000831566672891</v>
+        <v>0.1000831566672886</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234756909903204</v>
+        <v>1.234756909903205</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627075674957137</v>
+        <v>1.627075674957136</v>
       </c>
       <c r="F2" t="n">
-        <v>2.27550390078691e-46</v>
+        <v>2.275503900784375e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007543586664148222</v>
+        <v>0.007543586664148193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01785366274695305</v>
+        <v>0.01785366274695303</v>
       </c>
       <c r="D3" t="n">
         <v>-0.0274489493120042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04253612264030064</v>
+        <v>0.04253612264030059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6726431725489896</v>
+        <v>0.6726431725489905</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08746276072038492</v>
+        <v>-0.08746276072038491</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04650174918954324</v>
+        <v>0.04650174918954323</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1786045143500043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003678992909234485</v>
+        <v>0.003678992909234471</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05999248510483759</v>
+        <v>0.05999248510483754</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01403347829791832</v>
+        <v>-0.01403347829791828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03093697564115754</v>
+        <v>0.03093697564115752</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07466883634518004</v>
+        <v>-0.07466883634517997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04660187974934341</v>
+        <v>0.04660187974934342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6501059066201322</v>
+        <v>0.650105906620133</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.03787901042425931</v>
+        <v>-0.03787901042425914</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0320069596853672</v>
+        <v>0.03200695968536717</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1006114986622045</v>
+        <v>-0.1006114986622043</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02485347781368587</v>
+        <v>0.02485347781368597</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2366262230531381</v>
+        <v>0.23662622305314</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00379032924590907</v>
+        <v>0.003790329245909079</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02958199160697881</v>
+        <v>0.0295819916069788</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05418930889473555</v>
+        <v>-0.05418930889473552</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06176996738655369</v>
+        <v>0.06176996738655368</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8980463984756387</v>
+        <v>0.8980463984756384</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.009122079738841242</v>
+        <v>-0.009122079738841294</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03193143536141092</v>
+        <v>0.03193143536141091</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07170654302187536</v>
+        <v>-0.0717065430218754</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05346238354419287</v>
+        <v>0.05346238354419281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7751254483554763</v>
+        <v>0.775125448355475</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01941788401766656</v>
+        <v>0.01941788401766658</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03154682417714685</v>
+        <v>0.03154682417714684</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0424127551961587</v>
+        <v>-0.04241275519615866</v>
       </c>
       <c r="E9" t="n">
         <v>0.08124852323149181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5382075398620458</v>
+        <v>0.5382075398620453</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0104013495587579</v>
+        <v>0.01040134955875789</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05088991830122247</v>
+        <v>0.05088991830122239</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08934105748782391</v>
+        <v>-0.08934105748782377</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1101437566053397</v>
+        <v>0.1101437566053396</v>
       </c>
       <c r="F10" t="n">
         <v>0.8380493712142139</v>
@@ -1692,13 +1692,13 @@
         <v>-0.0716447838708316</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04908682432664914</v>
+        <v>0.04908682432664915</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1678531916665085</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0245636239248453</v>
+        <v>0.02456362392484532</v>
       </c>
       <c r="F11" t="n">
         <v>0.1444131763866514</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0855185319267842</v>
+        <v>-0.08551853192678424</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05175895972033011</v>
+        <v>0.05175895972033008</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1869642288558906</v>
+        <v>-0.1869642288558905</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01592716500232216</v>
+        <v>0.01592716500232207</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09848442135817068</v>
+        <v>0.09848442135817036</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02014219262295376</v>
+        <v>-0.0201421926229538</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04835193024820024</v>
+        <v>0.04835193024820021</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1149102344924191</v>
+        <v>-0.114910234492419</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07462584924651154</v>
+        <v>0.07462584924651144</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6769894910276891</v>
+        <v>0.6769894910276884</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04644002677660903</v>
+        <v>-0.04644002677660908</v>
       </c>
       <c r="C14" t="n">
         <v>0.04771229108737265</v>
@@ -1773,10 +1773,10 @@
         <v>-0.1399543989277509</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04707434537453279</v>
+        <v>0.04707434537453273</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3303869999996221</v>
+        <v>0.3303869999996215</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04379653132756456</v>
+        <v>-0.04379653132756453</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04846010907971655</v>
+        <v>0.04846010907971656</v>
       </c>
       <c r="D15" t="n">
         <v>-0.1387765998106915</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05118353715556234</v>
+        <v>0.0511835371555624</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3661202339272859</v>
+        <v>0.3661202339272863</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1817,16 +1817,16 @@
         <v>-0.04275936100726035</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04831280652572725</v>
+        <v>0.04831280652572715</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374507217897375</v>
+        <v>-0.1374507217897372</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05193199977521676</v>
+        <v>0.05193199977521656</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3761284191125531</v>
+        <v>0.376128419112552</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01894843278470501</v>
+        <v>-0.01894843278470502</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04870450629519191</v>
+        <v>0.0487045062951919</v>
       </c>
       <c r="D17" t="n">
         <v>-0.1144075110080855</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07651064543867547</v>
+        <v>0.07651064543867545</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972400008338187</v>
+        <v>0.6972400008338184</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03108663839834801</v>
+        <v>-0.03108663839834789</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0498078577707433</v>
+        <v>0.04980785777074326</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1287082457760984</v>
+        <v>-0.1287082457760982</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06653496897940231</v>
+        <v>0.06653496897940236</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5325414206392292</v>
+        <v>0.5325414206392306</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0367426440212983</v>
+        <v>-0.03674264402129831</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04885158569502038</v>
+        <v>0.04885158569502031</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1324899925712104</v>
+        <v>-0.1324899925712102</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05900470452861376</v>
+        <v>0.0590047045286136</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4519741045461788</v>
+        <v>0.4519741045461781</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.09057188359527769</v>
+        <v>-0.09057188359527762</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04927809434824124</v>
+        <v>0.04927809434824119</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1871551737445973</v>
+        <v>-0.1871551737445971</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00601140655404192</v>
+        <v>0.006011406554041893</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06606615464297572</v>
+        <v>0.0660661546429757</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006813317291130208</v>
+        <v>0.006813317291130233</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04829245253929011</v>
+        <v>0.04829245253929007</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0878381504109883</v>
+        <v>-0.08783815041098819</v>
       </c>
       <c r="E21" t="n">
         <v>0.1014647849932487</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8878031757662295</v>
+        <v>0.887803175766229</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006540046937606426</v>
+        <v>-0.006540046937606322</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04835474720397565</v>
+        <v>0.04835474720397571</v>
       </c>
       <c r="D22" t="n">
         <v>-0.1013136099389376</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08823351606372472</v>
+        <v>0.08823351606372495</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8924131142901419</v>
+        <v>0.8924131142901438</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1992,16 +1992,16 @@
         <v>-0.06600063754204354</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04797515526485328</v>
+        <v>0.04797515526485324</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1600302140138731</v>
+        <v>-0.160030214013873</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02802893892978604</v>
+        <v>0.02802893892978596</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1689066787636244</v>
+        <v>0.1689066787636242</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05334327025872957</v>
+        <v>-0.05334327025872958</v>
       </c>
       <c r="C24" t="n">
         <v>0.04069017585118596</v>
@@ -2023,10 +2023,10 @@
         <v>-0.1330945494516555</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02640800893419636</v>
+        <v>0.02640800893419634</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1898706359229398</v>
+        <v>0.1898706359229396</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006376847600652707</v>
+        <v>0.006376847600652669</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02353350465813144</v>
+        <v>0.02353350465813141</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03974797395929051</v>
+        <v>-0.03974797395929049</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05250166916059592</v>
+        <v>0.05250166916059583</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7864149607208579</v>
+        <v>0.7864149607208589</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0194313845026819</v>
+        <v>0.01943138450268204</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02857099835969376</v>
+        <v>0.02857099835969373</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03656674328467083</v>
+        <v>-0.03656674328467064</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07542951229003463</v>
+        <v>0.07542951229003472</v>
       </c>
       <c r="F26" t="n">
-        <v>0.49643563724821</v>
+        <v>0.4964356372482064</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01364006778452283</v>
+        <v>0.01364006778452286</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02987010641842527</v>
+        <v>0.02987010641842529</v>
       </c>
       <c r="D27" t="n">
         <v>-0.04490426500996941</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07218440057901507</v>
+        <v>0.07218440057901512</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6479254338860452</v>
+        <v>0.6479254338860447</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02905652978827477</v>
+        <v>0.02905652978827483</v>
       </c>
       <c r="C28" t="n">
         <v>0.0290407561001061</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02786230625174507</v>
+        <v>-0.027862306251745</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0859753658282946</v>
+        <v>0.08597536582829465</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3170477230932167</v>
+        <v>0.3170477230932155</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02046318562776316</v>
+        <v>-0.02046318562776314</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02907864115174509</v>
+        <v>0.0290786411517451</v>
       </c>
       <c r="D29" t="n">
         <v>-0.07745627500454785</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03652990374902153</v>
+        <v>0.03652990374902158</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4816079278891821</v>
+        <v>0.4816079278891827</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2176,7 +2176,7 @@
         <v>0.4728684571825822</v>
       </c>
       <c r="F30" t="n">
-        <v>4.491231826565502e-25</v>
+        <v>4.491231826565693e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.007538497370492831</v>
+        <v>0.0004763101673953236</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004040326219119737</v>
+        <v>0.00159428174403065</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0003803965047747392</v>
+        <v>-0.002648424632114455</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0154573912457604</v>
+        <v>0.003601044966905102</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06206738785508146</v>
+        <v>0.7651219509252104</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0004763101673953202</v>
+        <v>0.002452468964350139</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001594281744030681</v>
+        <v>0.001267934449779069</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00264842463211452</v>
+        <v>-3.263689197444738e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00360104496690516</v>
+        <v>0.004937574820674724</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7651219509252165</v>
+        <v>0.0530856198159608</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0006838861338531103</v>
+        <v>-0.0006838861338531105</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001270881981302642</v>
+        <v>0.001270881981302639</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003174769045807195</v>
+        <v>-0.003174769045807189</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001806996778100974</v>
+        <v>0.001806996778100968</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5904946825704056</v>
+        <v>0.5904946825704045</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002452468964350136</v>
+        <v>0.007538497370492838</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001267934449779067</v>
+        <v>0.004040326219119698</v>
       </c>
       <c r="D34" t="n">
-        <v>-3.263689197444478e-05</v>
+        <v>-0.0003803965047746577</v>
       </c>
       <c r="E34" t="n">
-        <v>0.004937574820674718</v>
+        <v>0.01545739124576033</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05308561981596056</v>
+        <v>0.06206738785507872</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2292,7 +2292,7 @@
         <v>0.579358867170089</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0104151000481304</v>
+        <v>0.01041510004813041</v>
       </c>
       <c r="D35" t="n">
         <v>0.558945646180372</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.158962193354871</v>
+        <v>-2.158962193354867</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5271718320277949</v>
+        <v>0.5271718320278143</v>
       </c>
       <c r="D2" t="n">
-        <v>4.21499909454871e-05</v>
+        <v>4.21499909455159e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0123840794946781</v>
+        <v>0.012384079494678</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1068934331327134</v>
+        <v>0.1068934331327136</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9077678991895131</v>
+        <v>0.9077678991895139</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.324061479874414</v>
+        <v>0.3240614798744141</v>
       </c>
       <c r="C4" t="n">
-        <v>0.230067342756592</v>
+        <v>0.2300673427565922</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589681126213354</v>
+        <v>0.1589681126213356</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7742552485596506</v>
+        <v>0.7742552485596507</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687090407132093</v>
+        <v>0.16870904071321</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4474942441877e-06</v>
+        <v>4.44749424418808e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1818685182700856</v>
+        <v>-0.1818685182700857</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2082512218159782</v>
+        <v>0.2082512218159788</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3824924469491958</v>
+        <v>0.3824924469491967</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1367270800884084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831182868961759</v>
+        <v>0.1831182868961763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4552688866476762</v>
+        <v>0.4552688866476772</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09668771677203519</v>
+        <v>-0.09668771677203515</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943986040042539</v>
+        <v>0.1943986040042545</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6189293064231929</v>
+        <v>0.6189293064231942</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.069744038116436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651181209928361</v>
+        <v>0.1651181209928366</v>
       </c>
       <c r="D9" t="n">
-        <v>9.254124082933939e-11</v>
+        <v>9.254124082935111e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1069802150572806</v>
+        <v>0.1069802150572799</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2832033016714789</v>
+        <v>0.2832033016714791</v>
       </c>
       <c r="D10" t="n">
-        <v>0.705615880078251</v>
+        <v>0.7056158800782533</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2579745235365333</v>
+        <v>0.2579745235365326</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2778622026713486</v>
+        <v>0.2778622026713496</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3531865806002399</v>
+        <v>0.3531865806002431</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1913836813322334</v>
+        <v>-0.1913836813322341</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3052132495597783</v>
+        <v>0.305213249559779</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5306270765800085</v>
+        <v>0.530627076580008</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3096324773489048</v>
+        <v>0.3096324773489042</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2734335275906097</v>
+        <v>0.2734335275906103</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2574719133643846</v>
+        <v>0.2574719133643865</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2686015457564107</v>
+        <v>0.26860154575641</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2611524565189018</v>
+        <v>0.2611524565189023</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3037034494888941</v>
+        <v>0.3037034494888962</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981954526051825</v>
+        <v>0.2981954526051819</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2676697859174158</v>
+        <v>0.267669785917417</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2652610583887277</v>
+        <v>0.2652610583887306</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1286082242724551</v>
+        <v>0.1286082242724544</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2547964366533378</v>
+        <v>0.2547964366533386</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6137352020167315</v>
+        <v>0.6137352020167346</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.187265922474091</v>
+        <v>0.1872659224740902</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2740865337717644</v>
+        <v>0.274086533771766</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4944574156002191</v>
+        <v>0.4944574156002235</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4792250424143022</v>
+        <v>0.4792250424143015</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542200639096521</v>
+        <v>0.2542200639096534</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05941909921850626</v>
+        <v>0.05941909921850794</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1174287321565227</v>
+        <v>0.117428732156522</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2802520220184872</v>
+        <v>0.2802520220184887</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6752079572031133</v>
+        <v>0.6752079572031167</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2512390302626729</v>
+        <v>0.2512390302626722</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2805131285650849</v>
+        <v>0.2805131285650856</v>
       </c>
       <c r="D20" t="n">
-        <v>0.370444585455746</v>
+        <v>0.3704445854557485</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2502097424803263</v>
+        <v>0.2502097424803256</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766872969776014</v>
+        <v>0.2766872969776036</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3658336265353836</v>
+        <v>0.3658336265353888</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001586873957917993</v>
+        <v>0.001586873957917211</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2917531392941569</v>
+        <v>0.2917531392941581</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9956602489653646</v>
+        <v>0.9956602489653669</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08094720439440929</v>
+        <v>-0.08094720439441005</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925914426201531</v>
+        <v>0.2925914426201542</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7820441915709209</v>
+        <v>0.7820441915709195</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8937956915905405</v>
+        <v>0.8937956915905404</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1584442431263436</v>
+        <v>0.1584442431263438</v>
       </c>
       <c r="D24" t="n">
-        <v>1.689927615944738e-08</v>
+        <v>1.689927615944812e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5765879163508648</v>
+        <v>-0.5765879163508649</v>
       </c>
       <c r="C25" t="n">
         <v>0.1158237616093812</v>
       </c>
       <c r="D25" t="n">
-        <v>6.419530711297054e-07</v>
+        <v>6.419530711297091e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1479699584837581</v>
+        <v>-0.147969958483758</v>
       </c>
       <c r="C26" t="n">
         <v>0.1535174480722673</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3351140594754034</v>
+        <v>0.3351140594754038</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0899482548834898</v>
+        <v>-0.08994825488348994</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1506886950402402</v>
+        <v>0.1506886950402403</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5505645198063103</v>
+        <v>0.5505645198063098</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05574640129887709</v>
+        <v>-0.05574640129887724</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1543104955024621</v>
+        <v>0.1543104955024623</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7179041641931153</v>
+        <v>0.717904164193115</v>
       </c>
     </row>
     <row r="29">
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3713220125545122</v>
+        <v>-0.3713220125545125</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1614980539979259</v>
+        <v>0.1614980539979262</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02149158647937501</v>
+        <v>0.02149158647937515</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01710601584298984</v>
+        <v>-0.01290875358535705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02271992637017727</v>
+        <v>0.008406891382953939</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4515051602521292</v>
+        <v>0.1246618784599245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01290875358535701</v>
+        <v>0.01401700440248824</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008406891382953788</v>
+        <v>0.006899535929054974</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1246618784599187</v>
+        <v>0.04219552933797057</v>
       </c>
     </row>
     <row r="32">
@@ -2830,29 +2830,29 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.007080910324510749</v>
+        <v>0.00708091032451073</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006267464118519504</v>
+        <v>0.006267464118519533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2585652583325001</v>
+        <v>0.2585652583325037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01401700440248826</v>
+        <v>-0.01710601584298991</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006899535929054942</v>
+        <v>0.02271992637017733</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04219552933796935</v>
+        <v>0.4515051602521285</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.03174935848357539</v>
+        <v>-0.03174935848357557</v>
       </c>
       <c r="C34" t="n">
-        <v>0.06037936443457578</v>
+        <v>0.0603793644345766</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5990054390834727</v>
+        <v>0.5990054390834756</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.095</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.015</v>
+        <v>-0.029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08</v>
+        <v>0.042</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02</v>
+        <v>-0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.018</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.024</v>
+        <v>0.369</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.362</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.216</v>
+        <v>-0.183</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.156</v>
+        <v>0.174</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.008</v>
+        <v>0.02</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.021</v>
+        <v>0.002</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.013</v>
+        <v>0.018</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.082</v>
+        <v>0.015</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.027</v>
+        <v>0.019</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05500000000000001</v>
+        <v>-0.004</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.117</v>
+        <v>0.008</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.003</v>
+        <v>0.005</v>
       </c>
       <c r="E13" t="n">
-        <v>0.114</v>
+        <v>0.003</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.015</v>
+        <v>-0.216</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>0.013</v>
+        <v>0.156</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.015</v>
+        <v>0.35</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.024</v>
+        <v>0.019</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.331</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.031</v>
+        <v>-0.082</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>-0.027</v>
       </c>
       <c r="E16" t="n">
-        <v>0.026</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.035</v>
+        <v>-0.117</v>
       </c>
       <c r="D17" t="n">
-        <v>0.024</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.114</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.003</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.099</v>
+        <v>0.19</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.024</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.35</v>
+        <v>0.024</v>
       </c>
       <c r="D20" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.331</v>
+        <v>0.02</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.036</v>
+        <v>0.099</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.045</v>
+        <v>-0.008</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006</v>
+        <v>-0.021</v>
       </c>
       <c r="E22" t="n">
-        <v>0.039</v>
+        <v>-0.013</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.183</v>
+        <v>-0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="E24" t="n">
-        <v>0.174</v>
+        <v>0.012</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.029</v>
+        <v>-0.005</v>
       </c>
       <c r="E25" t="n">
-        <v>0.042</v>
+        <v>0.026</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.369</v>
+        <v>0.003</v>
       </c>
       <c r="D26" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.362</v>
+        <v>0.003</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.011</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.006999999999999999</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.003</v>
+        <v>-0.015</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E28" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="D29" t="n">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.004</v>
+        <v>0.03</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.018</v>
+        <v>0.045</v>
       </c>
       <c r="D30" t="n">
         <v>0.006</v>
       </c>
       <c r="E30" t="n">
-        <v>0.012</v>
+        <v>0.039</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.19</v>
+        <v>-0.015</v>
       </c>
       <c r="D31" t="n">
-        <v>0.024</v>
+        <v>-0.024</v>
       </c>
       <c r="E31" t="n">
-        <v>0.166</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9949908017929653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.165743902389888</v>
+        <v>0.1657439023898879</v>
       </c>
       <c r="E2" t="n">
-        <v>1.853163385476146</v>
+        <v>1.853163385476145</v>
       </c>
       <c r="F2" t="n">
         <v>1.168712646832276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.851455159122649</v>
+        <v>1.851455159122647</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.43091629243017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1000831566672887</v>
+        <v>0.1000831566672874</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234756909903204</v>
+        <v>1.234756909903207</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627075674957136</v>
+        <v>1.627075674957133</v>
       </c>
       <c r="F2" t="n">
-        <v>2.275503900784928e-46</v>
+        <v>2.275503900779111e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007543586664148233</v>
+        <v>0.007543586664148225</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01785366274695303</v>
+        <v>0.01785366274695304</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02744894931200416</v>
+        <v>-0.02744894931200418</v>
       </c>
       <c r="E3" t="n">
         <v>0.04253612264030063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.672643172548989</v>
+        <v>0.6726431725489894</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08746276072038491</v>
+        <v>-0.08746276072038493</v>
       </c>
       <c r="C4" t="n">
         <v>0.04650174918954324</v>
@@ -1523,10 +1523,10 @@
         <v>-0.1786045143500043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003678992909234485</v>
+        <v>0.003678992909234458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05999248510483759</v>
+        <v>0.05999248510483754</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01403347829791827</v>
+        <v>-0.0140334782979183</v>
       </c>
       <c r="C5" t="n">
         <v>0.03093697564115752</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07466883634517996</v>
+        <v>-0.07466883634518</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04660187974934342</v>
+        <v>0.04660187974934339</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6501059066201332</v>
+        <v>0.6501059066201325</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.03787901042425911</v>
+        <v>-0.03787901042425924</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03200695968536717</v>
+        <v>0.03200695968536719</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1006114986622042</v>
+        <v>-0.1006114986622044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.024853477813686</v>
+        <v>0.02485347781368591</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2366262230531401</v>
+        <v>0.2366262230531389</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003790329245909075</v>
+        <v>0.003790329245909049</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02958199160697878</v>
+        <v>0.0295819916069788</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05418930889473549</v>
+        <v>-0.05418930889473556</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06176996738655364</v>
+        <v>0.06176996738655365</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8980463984756385</v>
+        <v>0.8980463984756393</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.009122079738841243</v>
+        <v>-0.009122079738841252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03193143536141089</v>
+        <v>0.03193143536141092</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0717065430218753</v>
+        <v>-0.07170654302187537</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05346238354419282</v>
+        <v>0.05346238354419287</v>
       </c>
       <c r="F8" t="n">
         <v>0.7751254483554759</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01941788401766657</v>
+        <v>0.01941788401766658</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03154682417714683</v>
+        <v>0.03154682417714684</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04241275519615863</v>
+        <v>-0.04241275519615866</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08124852323149179</v>
+        <v>0.08124852323149181</v>
       </c>
       <c r="F9" t="n">
         <v>0.5382075398620452</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01040134955875787</v>
+        <v>0.01040134955875788</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05088991830122237</v>
+        <v>0.0508899183012223</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08934105748782373</v>
+        <v>-0.08934105748782359</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1101437566053395</v>
+        <v>0.1101437566053393</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8380493712142139</v>
+        <v>0.8380493712142136</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07164478387083152</v>
+        <v>-0.07164478387083155</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04908682432664907</v>
+        <v>0.04908682432664901</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1678531916665083</v>
+        <v>-0.1678531916665082</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02456362392484525</v>
+        <v>0.02456362392484511</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1444131763866513</v>
+        <v>0.1444131763866507</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08551853192678413</v>
+        <v>-0.08551853192678412</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05175895972032998</v>
+        <v>0.05175895972032988</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1869642288558903</v>
+        <v>-0.18696422885589</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01592716500232198</v>
+        <v>0.01592716500232179</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09848442135817009</v>
+        <v>0.09848442135816948</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02014219262295373</v>
+        <v>-0.0201421926229537</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04835193024820026</v>
+        <v>0.04835193024820014</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1149102344924191</v>
+        <v>-0.1149102344924188</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07462584924651161</v>
+        <v>0.07462584924651143</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6769894910276896</v>
+        <v>0.6769894910276895</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04644002677660915</v>
+        <v>-0.04644002677660895</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04771229108737265</v>
+        <v>0.04771229108737251</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.139954398927751</v>
+        <v>-0.1399543989277505</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04707434537453267</v>
+        <v>0.04707434537453258</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3303869999996208</v>
+        <v>0.3303869999996214</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04379653132756453</v>
+        <v>-0.0437965313275645</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04846010907971652</v>
+        <v>0.04846010907971653</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1387765998106914</v>
+        <v>-0.1387765998106913</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05118353715556231</v>
+        <v>0.05118353715556236</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3661202339272859</v>
+        <v>0.3661202339272863</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0427593610072603</v>
+        <v>-0.04275936100726032</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04831280652572716</v>
+        <v>0.04831280652572709</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374507217897372</v>
+        <v>-0.1374507217897371</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05193199977521663</v>
+        <v>0.05193199977521647</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3761284191125529</v>
+        <v>0.3761284191125518</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1842,16 +1842,16 @@
         <v>-0.01894843278470496</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0487045062951918</v>
+        <v>0.04870450629519173</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1144075110080852</v>
+        <v>-0.1144075110080851</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07651064543867532</v>
+        <v>0.07651064543867517</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972400008338189</v>
+        <v>0.6972400008338184</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03108663839834802</v>
+        <v>-0.03108663839834786</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04980785777074322</v>
+        <v>0.04980785777074329</v>
       </c>
       <c r="D18" t="n">
         <v>-0.1287082457760982</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06653496897940214</v>
+        <v>0.06653496897940245</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5325414206392285</v>
+        <v>0.5325414206392313</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03674264402129819</v>
+        <v>-0.03674264402129824</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04885158569502028</v>
+        <v>0.04885158569502022</v>
       </c>
       <c r="D19" t="n">
         <v>-0.13248999257121</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05900470452861366</v>
+        <v>0.05900470452861351</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4519741045461791</v>
+        <v>0.4519741045461783</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1917,16 +1917,16 @@
         <v>-0.09057188359527761</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04927809434824119</v>
+        <v>0.0492780943482411</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1871551737445971</v>
+        <v>-0.1871551737445969</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006011406554041906</v>
+        <v>0.006011406554041726</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0660661546429757</v>
+        <v>0.0660661546429752</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006813317291130298</v>
+        <v>0.006813317291130285</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04829245253929003</v>
+        <v>0.04829245253928997</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08783815041098804</v>
+        <v>-0.08783815041098794</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1014647849932486</v>
+        <v>0.1014647849932485</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8878031757662278</v>
+        <v>0.8878031757662279</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006540046937606202</v>
+        <v>-0.00654004693760626</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0483547472039756</v>
+        <v>0.04835474720397558</v>
       </c>
       <c r="D22" t="n">
         <v>-0.1013136099389373</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08823351606372487</v>
+        <v>0.08823351606372475</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8924131142901455</v>
+        <v>0.8924131142901445</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06600063754204349</v>
+        <v>-0.06600063754204347</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04797515526485321</v>
+        <v>0.04797515526485312</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1600302140138729</v>
+        <v>-0.1600302140138727</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02802893892978595</v>
+        <v>0.02802893892978581</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1689066787636242</v>
+        <v>0.1689066787636234</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05334327025872956</v>
+        <v>-0.05334327025872958</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04069017585118595</v>
+        <v>0.04069017585118598</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1330945494516555</v>
+        <v>-0.1330945494516556</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02640800893419635</v>
+        <v>0.02640800893419638</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1898706359229397</v>
+        <v>0.1898706359229398</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006376847600652705</v>
+        <v>0.006376847600652682</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02353350465813138</v>
+        <v>0.02353350465813141</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0397479739592904</v>
+        <v>-0.03974797395929049</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05250166916059582</v>
+        <v>0.05250166916059584</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7864149607208575</v>
+        <v>0.7864149607208586</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01943138450268201</v>
+        <v>0.01943138450268189</v>
       </c>
       <c r="C26" t="n">
         <v>0.02857099835969373</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03656674328467065</v>
+        <v>-0.03656674328467079</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07542951229003468</v>
+        <v>0.07542951229003457</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4964356372482069</v>
+        <v>0.4964356372482097</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01364006778452284</v>
+        <v>0.01364006778452285</v>
       </c>
       <c r="C27" t="n">
         <v>0.02987010641842526</v>
@@ -2098,10 +2098,10 @@
         <v>-0.04490426500996937</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07218440057901505</v>
+        <v>0.07218440057901507</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6479254338860448</v>
+        <v>0.6479254338860445</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02905652978827489</v>
+        <v>0.02905652978827478</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02904075610010612</v>
+        <v>0.0290407561001061</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02786230625174499</v>
+        <v>-0.02786230625174506</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08597536582829476</v>
+        <v>0.08597536582829461</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3170477230932151</v>
+        <v>0.3170477230932165</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02046318562776315</v>
+        <v>-0.02046318562776314</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02907864115174509</v>
+        <v>0.02907864115174506</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07745627500454785</v>
+        <v>-0.07745627500454777</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03652990374902156</v>
+        <v>0.03652990374902149</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4816079278891824</v>
+        <v>0.4816079278891819</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3975380272033305</v>
+        <v>0.3975380272033306</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03843459909133462</v>
+        <v>0.03843459909133459</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3222075972240788</v>
+        <v>0.3222075972240789</v>
       </c>
       <c r="E30" t="n">
         <v>0.4728684571825823</v>
       </c>
       <c r="F30" t="n">
-        <v>4.491231826565693e-25</v>
+        <v>4.491231826565276e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2192,7 +2192,7 @@
         <v>0.579358867170089</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01041510004813033</v>
+        <v>0.01041510004813034</v>
       </c>
       <c r="D31" t="n">
         <v>0.5589456461803721</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002452468964350139</v>
+        <v>-0.0006838861338531079</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001267934449779068</v>
+        <v>0.001270881981302642</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.263689197444434e-05</v>
+        <v>-0.003174769045807191</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004937574820674721</v>
+        <v>0.001806996778100976</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05308561981596054</v>
+        <v>0.5904946825704067</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00753849737049284</v>
+        <v>0.007538497370492823</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004040326219119724</v>
+        <v>0.004040326219119732</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0003803965047747071</v>
+        <v>-0.0003803965047747384</v>
       </c>
       <c r="E33" t="n">
         <v>0.01545739124576039</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06206738785508031</v>
+        <v>0.06206738785508146</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0004763101673953283</v>
+        <v>0.0004763101673953255</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001594281744030654</v>
+        <v>0.001594281744030625</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.002648424632114459</v>
+        <v>-0.002648424632114404</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003601044966905116</v>
+        <v>0.003601044966905055</v>
       </c>
       <c r="F34" t="n">
-        <v>0.765121950925209</v>
+        <v>0.765121950925206</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0006838861338531097</v>
+        <v>0.002452468964350139</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00127088198130264</v>
+        <v>0.001267934449779069</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003174769045807191</v>
+        <v>-3.263689197444651e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001806996778100972</v>
+        <v>0.004937574820674724</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5904946825704056</v>
+        <v>0.05308561981596073</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.158962193354869</v>
+        <v>-2.158962193354871</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5271718320278008</v>
+        <v>0.5271718320277896</v>
       </c>
       <c r="D2" t="n">
-        <v>4.21499909454961e-05</v>
+        <v>4.214999094547929e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0123840794946781</v>
+        <v>0.01238407949467822</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1068934331327136</v>
+        <v>0.1068934331327135</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9077678991895132</v>
+        <v>0.9077678991895122</v>
       </c>
     </row>
     <row r="4">
@@ -2388,7 +2388,7 @@
         <v>0.2300673427565921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589681126213355</v>
+        <v>0.1589681126213353</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7742552485596508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687090407132096</v>
+        <v>0.1687090407132095</v>
       </c>
       <c r="D5" t="n">
-        <v>4.447494244187851e-06</v>
+        <v>4.447494244187784e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2417,10 +2417,10 @@
         <v>-0.1818685182700855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2082512218159785</v>
+        <v>0.2082512218159784</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3824924469491968</v>
+        <v>0.3824924469491962</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1367270800884084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831182868961761</v>
+        <v>0.183118286896176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4552688866476763</v>
+        <v>0.4552688866476758</v>
       </c>
     </row>
     <row r="8">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09668771677203518</v>
+        <v>-0.0966877167720351</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943986040042542</v>
+        <v>0.1943986040042541</v>
       </c>
       <c r="D8" t="n">
         <v>0.6189293064231935</v>
@@ -2465,10 +2465,10 @@
         <v>1.069744038116436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651181209928363</v>
+        <v>0.1651181209928362</v>
       </c>
       <c r="D9" t="n">
-        <v>9.254124082934272e-11</v>
+        <v>9.254124082934172e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2481,7 +2481,7 @@
         <v>0.1069802150572807</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2832033016714788</v>
+        <v>0.2832033016714787</v>
       </c>
       <c r="D10" t="n">
         <v>0.7056158800782508</v>
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2579745235365333</v>
+        <v>0.2579745235365336</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2778622026713496</v>
+        <v>0.2778622026713491</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3531865806002417</v>
+        <v>0.3531865806002403</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1913836813322334</v>
+        <v>-0.191383681332233</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3052132495597789</v>
+        <v>0.3052132495597792</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5306270765800092</v>
+        <v>0.5306270765800105</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3096324773489049</v>
+        <v>0.3096324773489051</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2734335275906097</v>
+        <v>0.2734335275906108</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2574719133643845</v>
+        <v>0.2574719133643859</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2686015457564107</v>
+        <v>0.268601545756411</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2611524565189028</v>
+        <v>0.2611524565189025</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3037034494888959</v>
+        <v>0.3037034494888947</v>
       </c>
     </row>
     <row r="15">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981954526051826</v>
+        <v>0.2981954526051829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2676697859174169</v>
+        <v>0.2676697859174172</v>
       </c>
       <c r="D15" t="n">
         <v>0.2652610583887295</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1286082242724551</v>
+        <v>0.1286082242724556</v>
       </c>
       <c r="C16" t="n">
         <v>0.2547964366533388</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6137352020167328</v>
+        <v>0.6137352020167317</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1872659224740909</v>
+        <v>0.1872659224740912</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2740865337717657</v>
+        <v>0.2740865337717647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4944574156002216</v>
+        <v>0.4944574156002191</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4792250424143021</v>
+        <v>0.4792250424143028</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542200639096531</v>
+        <v>0.2542200639096532</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05941909921850728</v>
+        <v>0.05941909921850706</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1174287321565226</v>
+        <v>0.1174287321565229</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2802520220184888</v>
+        <v>0.2802520220184874</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6752079572031152</v>
+        <v>0.6752079572031128</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2512390302626727</v>
+        <v>0.2512390302626731</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2805131285650854</v>
+        <v>0.2805131285650848</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3704445854557469</v>
+        <v>0.3704445854557453</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2502097424803263</v>
+        <v>0.2502097424803267</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766872969776032</v>
+        <v>0.2766872969776031</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3658336265353869</v>
+        <v>0.3658336265353858</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001586873957917985</v>
+        <v>0.001586873957918478</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2917531392941587</v>
+        <v>0.2917531392941579</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9956602489653648</v>
+        <v>0.9956602489653633</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08094720439440953</v>
+        <v>-0.08094720439440919</v>
       </c>
       <c r="C23" t="n">
         <v>0.2925914426201544</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7820441915709211</v>
+        <v>0.782044191570922</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8937956915905404</v>
+        <v>0.8937956915905406</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1584442431263438</v>
+        <v>0.1584442431263437</v>
       </c>
       <c r="D24" t="n">
-        <v>1.689927615944801e-08</v>
+        <v>1.68992761594477e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5765879163508649</v>
+        <v>-0.5765879163508647</v>
       </c>
       <c r="C25" t="n">
         <v>0.1158237616093811</v>
       </c>
       <c r="D25" t="n">
-        <v>6.419530711296864e-07</v>
+        <v>6.419530711297008e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2737,10 +2737,10 @@
         <v>-0.147969958483758</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1535174480722672</v>
+        <v>0.1535174480722675</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3351140594754038</v>
+        <v>0.3351140594754047</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08994825488348984</v>
+        <v>-0.08994825488348961</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1506886950402402</v>
+        <v>0.1506886950402403</v>
       </c>
       <c r="D27" t="n">
-        <v>0.55056451980631</v>
+        <v>0.5505645198063112</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0557464012988771</v>
+        <v>-0.05574640129887686</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1543104955024624</v>
+        <v>0.1543104955024622</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7179041641931159</v>
+        <v>0.7179041641931165</v>
       </c>
     </row>
     <row r="29">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3713220125545124</v>
+        <v>-0.3713220125545121</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1614980539979261</v>
+        <v>0.1614980539979262</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02149158647937512</v>
+        <v>0.0214915864793753</v>
       </c>
     </row>
     <row r="30">
@@ -2798,29 +2798,29 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.03174935848357564</v>
+        <v>-0.03174935848357546</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06037936443457633</v>
+        <v>0.06037936443457656</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5990054390834731</v>
+        <v>0.5990054390834767</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01401700440248825</v>
+        <v>0.007080910324510751</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006899535929054955</v>
+        <v>0.006267464118519483</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0421955293379699</v>
+        <v>0.2585652583324984</v>
       </c>
     </row>
     <row r="32">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01710601584298987</v>
+        <v>-0.01710601584298988</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02271992637017747</v>
+        <v>0.02271992637017742</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4515051602521324</v>
+        <v>0.4515051602521311</v>
       </c>
     </row>
     <row r="33">
@@ -2846,29 +2846,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01290875358535703</v>
+        <v>-0.012908753585357</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008406891382953762</v>
+        <v>0.008406891382953684</v>
       </c>
       <c r="D33" t="n">
-        <v>0.124661878459917</v>
+        <v>0.1246618784599146</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.007080910324510735</v>
+        <v>0.01401700440248826</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006267464118519493</v>
+        <v>0.006899535929054983</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2585652583325003</v>
+        <v>0.04219552933797059</v>
       </c>
     </row>
   </sheetData>
